--- a/3_작업영역/0_테이블/테이블.xlsx
+++ b/3_작업영역/0_테이블/테이블.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Awsintel4 Repository\K_dessert\3_작업영역\0_테이블\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AWSsintel4_Repository\K_dessert\3_작업영역\0_테이블\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D27648D4-1F0A-4B0F-B424-C3A5BB743019}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{010EC0E3-66B4-4403-BA84-9DF3E0CAD156}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{89506D57-ACF2-4766-BACF-4F8058B8758D}"/>
+    <workbookView xWindow="6270" yWindow="30" windowWidth="21660" windowHeight="15060" xr2:uid="{89506D57-ACF2-4766-BACF-4F8058B8758D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="37">
   <si>
     <t>index</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -169,6 +169,18 @@
   </si>
   <si>
     <t>디저트-태그테이블</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>조회수</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이미지</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>타입(필터링)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -201,7 +213,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -224,13 +236,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -238,6 +261,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -563,7 +589,7 @@
     <col min="4" max="4" width="7.5" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11.875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.25" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="5.25" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.375" customWidth="1"/>
     <col min="9" max="9" width="16.625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="8.5" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.75" bestFit="1" customWidth="1"/>
@@ -693,7 +719,7 @@
       </c>
       <c r="B16" s="1"/>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>19</v>
       </c>
@@ -701,7 +727,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>23</v>
       </c>
@@ -709,7 +735,7 @@
       <c r="C19" s="1"/>
       <c r="D19" s="1"/>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>0</v>
       </c>
@@ -723,13 +749,13 @@
         <v>25</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>26</v>
       </c>
       <c r="B22" s="1"/>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>17</v>
       </c>
@@ -737,7 +763,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>29</v>
       </c>
@@ -745,7 +771,7 @@
       <c r="C25" s="1"/>
       <c r="D25" s="1"/>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
         <v>0</v>
       </c>
@@ -758,14 +784,23 @@
       <c r="D26" s="1" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E26" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
         <v>33</v>
       </c>
       <c r="B28" s="1"/>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
         <v>30</v>
       </c>

--- a/3_작업영역/0_테이블/테이블.xlsx
+++ b/3_작업영역/0_테이블/테이블.xlsx
@@ -3,19 +3,15 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AWSsintel4_Repository\K_dessert\3_작업영역\0_테이블\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{010EC0E3-66B4-4403-BA84-9DF3E0CAD156}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{7F9394F8-428B-4356-8753-A75FA3A8C699}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6270" yWindow="30" windowWidth="21660" windowHeight="15060" xr2:uid="{89506D57-ACF2-4766-BACF-4F8058B8758D}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="21690" windowHeight="16500" xr2:uid="{89506D57-ACF2-4766-BACF-4F8058B8758D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="0"/>
+  <oleSize ref="A1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -34,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="67">
   <si>
     <t>index</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -68,10 +64,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>m_address</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>o_address</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -108,10 +100,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>p_productor</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>t_id</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -181,6 +169,134 @@
   </si>
   <si>
     <t>타입(필터링)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>인덱스</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이름</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>연락처</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이메일</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가입일</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본키</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>주문번호</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>회원인덱스</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>주문 주소</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>외래키</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>주문일시</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>상품인덱스</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>상품-주문테이블</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>상품번호</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>상품ID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>상품명</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>상품가격</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>재고</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>태그인덱스</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>태그ID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>태그이름</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>제품ID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>넣은 재고</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>디저트 인덱스</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>설명</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>VIEW_TIME</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>IMG</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TYPE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>고유키</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>디저트id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>태그id</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -253,7 +369,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -264,6 +380,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -580,7 +702,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1EC1A73-CE70-4415-A446-32DCA71A6530}">
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G50"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.625" bestFit="1" customWidth="1"/>
@@ -599,213 +721,417 @@
     <col min="16" max="16" width="9.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G2" s="1" t="s">
+      <c r="E3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+    </row>
+    <row r="6" spans="1:7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+    </row>
+    <row r="7" spans="1:7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+        <v>42</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+    </row>
+    <row r="12" spans="1:7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C13" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="4"/>
+      <c r="B14" s="4"/>
+      <c r="C14" s="4"/>
+    </row>
+    <row r="15" spans="1:7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B15" s="1"/>
+      <c r="C15" s="4"/>
+    </row>
+    <row r="16" spans="1:7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C16" s="4"/>
+    </row>
+    <row r="17" spans="1:7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B17" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="1" t="s">
+      <c r="C17" s="4"/>
+    </row>
+    <row r="18" spans="1:7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="C18" s="4"/>
+    </row>
+    <row r="19" spans="1:7" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="20" spans="1:7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B20" s="1"/>
+      <c r="C20" s="1"/>
+      <c r="D20" s="1"/>
+    </row>
+    <row r="21" spans="1:7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B22" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
+      <c r="C22" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B23" s="4"/>
+      <c r="C23" s="4"/>
+      <c r="D23" s="4"/>
+      <c r="E23" s="5"/>
+    </row>
+    <row r="24" spans="1:7" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="25" spans="1:7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B25" s="1"/>
+    </row>
+    <row r="26" spans="1:7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B27" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D11" s="1" t="s">
+    </row>
+    <row r="28" spans="1:7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="30" spans="1:7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B30" s="1"/>
+    </row>
+    <row r="31" spans="1:7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="34" spans="1:7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B34" s="1"/>
+      <c r="C34" s="1"/>
+      <c r="D34" s="1"/>
+    </row>
+    <row r="35" spans="1:7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="37" spans="1:7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B37" s="1"/>
+    </row>
+    <row r="38" spans="1:7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E11" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F11" s="2" t="s">
+      <c r="B39" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B40" s="4"/>
+    </row>
+    <row r="42" spans="1:7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="1" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B13" s="1"/>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B16" s="1"/>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A17" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A19" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B19" s="1"/>
-      <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A20" s="1" t="s">
+      <c r="B42" s="1"/>
+      <c r="C42" s="1"/>
+      <c r="D42" s="1"/>
+      <c r="E42" s="1"/>
+      <c r="F42" s="1"/>
+      <c r="G42" s="1"/>
+    </row>
+    <row r="43" spans="1:7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F43" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G43" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B20" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A22" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B22" s="1"/>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A23" s="1" t="s">
+      <c r="B44" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="G44" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="5" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="47" spans="1:7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B47" s="1"/>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A48" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A49" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B49" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B23" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A25" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B25" s="1"/>
-      <c r="C25" s="1"/>
-      <c r="D25" s="1"/>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A26" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A28" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B28" s="1"/>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A29" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>19</v>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A50" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>45</v>
       </c>
     </row>
   </sheetData>

--- a/3_작업영역/0_테이블/테이블.xlsx
+++ b/3_작업영역/0_테이블/테이블.xlsx
@@ -3,34 +3,29 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{7F9394F8-428B-4356-8753-A75FA3A8C699}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Awsintel4 Repository\AwsIntel4_OWR\K_dessert\3_작업영역\0_테이블\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0400D3DC-D215-46A9-AF29-0DA5D127F9F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="21690" windowHeight="16500" xr2:uid="{89506D57-ACF2-4766-BACF-4F8058B8758D}"/>
+    <workbookView xWindow="270" yWindow="1905" windowWidth="15510" windowHeight="13920" xr2:uid="{89506D57-ACF2-4766-BACF-4F8058B8758D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
-  <oleSize ref="A1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="103">
   <si>
     <t>index</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -40,14 +35,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>name</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>phone</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>m_index</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -60,10 +47,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>time</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>o_address</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -80,10 +63,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>email</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>상품정보 테이블</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -176,10 +155,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>ID</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>이름</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -297,6 +272,170 @@
   </si>
   <si>
     <t>태그id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>패스워드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sysdate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>애매함</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>작성자ID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>제목</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>텍스트</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>회원ID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>o_status</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>처리상태</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>member</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>member_order</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>product_order</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>product</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>product_tag</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tag</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>basket</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>desert</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>desert_tag</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NUMBER(6)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>VARCHAR2(20)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>VARCHAR2(100)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DATE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M_index</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>m_id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M_password</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M_NAME</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M_phone</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M_email</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M_SIGN_TIME</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>o_time</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>주문 연락처</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>o_phone</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>남기는 말</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>o_comment</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>VARCHAR2(4000)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>상품 설명</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>p_intro</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>t_index</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NUMBER(2)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>d_index</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>s_order</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -359,7 +498,9 @@
       <right style="thin">
         <color indexed="64"/>
       </right>
-      <top/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
@@ -379,13 +520,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -702,16 +843,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1EC1A73-CE70-4415-A446-32DCA71A6530}">
-  <dimension ref="A1:G50"/>
+  <dimension ref="A1:G65"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.75" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.25" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.375" customWidth="1"/>
+    <col min="1" max="1" width="18" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="14.875" bestFit="1" customWidth="1"/>
+    <col min="4" max="6" width="16" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="16.625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="8.5" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.75" bestFit="1" customWidth="1"/>
@@ -721,418 +859,594 @@
     <col min="16" max="16" width="9.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" s="4"/>
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A16" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B17" s="1"/>
+      <c r="C17" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D17" s="1"/>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A18" s="3"/>
+      <c r="B18" s="3"/>
+      <c r="C18" s="3"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A19" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C19" s="3"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A20" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C20" s="3"/>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A21" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C21" s="3"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A22" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C22" s="3"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A23" s="4"/>
+      <c r="B23" s="4"/>
+      <c r="C23" s="3"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A25" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C25" s="1"/>
+      <c r="D25" s="1"/>
+      <c r="E25" s="1"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A26" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A27" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C27" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-    </row>
-    <row r="2" spans="1:7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B2" s="1" t="s">
+      <c r="D27" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A28" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F2" s="1" t="s">
+      <c r="B28" s="1"/>
+      <c r="C28" s="1"/>
+      <c r="D28" s="1"/>
+      <c r="E28" s="2"/>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A30" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A31" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A32" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A33" s="2" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="1" t="s">
+      <c r="B33" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A35" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A36" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A37" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A38" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A39" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A42" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A43" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A44" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A45" s="1"/>
+      <c r="B45" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A46" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B46" s="1"/>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A48" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C48" s="1"/>
+      <c r="D48" s="1"/>
+      <c r="E48" s="1"/>
+      <c r="F48" s="1"/>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A49" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F49" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A50" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="F50" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A51" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C51" s="1"/>
+      <c r="D51" s="2"/>
+      <c r="E51" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="F51" s="1"/>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A52" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B52" s="1"/>
+      <c r="C52" s="1"/>
+      <c r="D52" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E52" s="1"/>
+      <c r="F52" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A54" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A55" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A56" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A57" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A62" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B62" s="1"/>
+      <c r="C62" s="1"/>
+      <c r="D62" s="1"/>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A63" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A64" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B64" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-    </row>
-    <row r="6" spans="1:7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-    </row>
-    <row r="7" spans="1:7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-    </row>
-    <row r="12" spans="1:7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="4"/>
-      <c r="B14" s="4"/>
-      <c r="C14" s="4"/>
-    </row>
-    <row r="15" spans="1:7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B15" s="1"/>
-      <c r="C15" s="4"/>
-    </row>
-    <row r="16" spans="1:7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C16" s="4"/>
-    </row>
-    <row r="17" spans="1:7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C17" s="4"/>
-    </row>
-    <row r="18" spans="1:7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="C18" s="4"/>
-    </row>
-    <row r="19" spans="1:7" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="20" spans="1:7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B20" s="1"/>
-      <c r="C20" s="1"/>
-      <c r="D20" s="1"/>
-    </row>
-    <row r="21" spans="1:7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B23" s="4"/>
-      <c r="C23" s="4"/>
-      <c r="D23" s="4"/>
-      <c r="E23" s="5"/>
-    </row>
-    <row r="24" spans="1:7" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="25" spans="1:7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B25" s="1"/>
-    </row>
-    <row r="26" spans="1:7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B28" s="4" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="30" spans="1:7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="1" t="s">
+      <c r="C64" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B30" s="1"/>
-    </row>
-    <row r="31" spans="1:7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B32" s="1" t="s">
+      <c r="D64" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="33" spans="1:7" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="34" spans="1:7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B34" s="1"/>
-      <c r="C34" s="1"/>
-      <c r="D34" s="1"/>
-    </row>
-    <row r="35" spans="1:7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="37" spans="1:7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B37" s="1"/>
-    </row>
-    <row r="38" spans="1:7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B40" s="4"/>
-    </row>
-    <row r="42" spans="1:7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B42" s="1"/>
-      <c r="C42" s="1"/>
-      <c r="D42" s="1"/>
-      <c r="E42" s="1"/>
-      <c r="F42" s="1"/>
-      <c r="G42" s="1"/>
-    </row>
-    <row r="43" spans="1:7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B43" s="1" t="s">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A65" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C43" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="D43" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="E43" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="F43" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="G43" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D44" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="F44" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="G44" s="2" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="5" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="47" spans="1:7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B47" s="1"/>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A48" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A49" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A50" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>45</v>
-      </c>
+      <c r="B65" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C65" s="1"/>
+      <c r="D65" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/3_작업영역/0_테이블/테이블.xlsx
+++ b/3_작업영역/0_테이블/테이블.xlsx
@@ -3,19 +3,16 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Awsintel4 Repository\AwsIntel4_OWR\K_dessert\3_작업영역\0_테이블\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0400D3DC-D215-46A9-AF29-0DA5D127F9F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{BC93BC09-B44B-4D61-890B-39D903D607B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="270" yWindow="1905" windowWidth="15510" windowHeight="13920" xr2:uid="{89506D57-ACF2-4766-BACF-4F8058B8758D}"/>
+    <workbookView xWindow="13845" yWindow="1455" windowWidth="15540" windowHeight="16500" activeTab="1" xr2:uid="{89506D57-ACF2-4766-BACF-4F8058B8758D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
+  <oleSize ref="A1:U30"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -25,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="438" uniqueCount="189">
   <si>
     <t>index</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -436,6 +433,349 @@
   </si>
   <si>
     <t>s_order</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MEMBER</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>처리상태 테이블</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>STATUS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>컬럼명</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>포맷</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>비고</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M_INDEX</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PRIMARY KEY</t>
+  </si>
+  <si>
+    <t>처리인덱스</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>STA_INDEX</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M_ID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UNIQUE NOT NULL</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">처리상태 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>STA_STATUS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>VARCHAR2(255)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M_PASSWORD</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NOT NULL</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>게시판테이블</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FREE_BOARD</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M_TEL</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M_EMAIL</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>게시판 인덱스</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>F_index</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>주소</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M_ADDRESS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FOREIGN KEY</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>상세주소</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M_ADDRESS_SEC</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>F_SUBJECT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>VARCHAR2(200)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DEFAULT SYSDATE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>F_TEXT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TEXT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>포인트</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M_POINT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NUMBER(9)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>작성일</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>F_CRE_DATE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>공지여부</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>F_NOTICE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MEMBER_ORDER</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>O_INDEX</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>답변테이블</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>REPLY</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>R_INDEX</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PRIMARY KEY</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>S_ORDER</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>R_TEXT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>F_INDEX</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>R_CRE_DATE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>O_TIME</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>다과정보테이블</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DESSERT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>주소_상세</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>다과 인덱스</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>D_INDEX</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>D_NAME</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>O_COMMENT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>D_TEXT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>D_IMAGE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PRODUCT_ORDER</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>D_VIEW</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>공개여부</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>P_OPEN</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DEFAULT '공개'</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>P_INDEX</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DESSERT_TAG</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>주문개수</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PO_STOCK</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>T_INDEX</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PRODUCT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PRODUCT_TAG</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>P_NAME</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>P_PRICE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>P_STOCK</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DEFAULT 0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>P_INTRO</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TAG</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>상품이미지</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>P_IMAGE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BASKET</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>T_NAME</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>장바구니 인덱스</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>B_INDEX</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>회원 인덱스</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>B_STOCK</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -468,7 +808,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -499,6 +839,164 @@
         <color indexed="64"/>
       </right>
       <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
         <color indexed="64"/>
       </top>
       <bottom/>
@@ -510,7 +1008,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -527,6 +1025,42 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1453,4 +1987,1105 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87580854-C28E-4E95-AB15-75B01A5EA365}">
+  <dimension ref="B2:BE54"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="3.25" customWidth="1"/>
+    <col min="2" max="2" width="18" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.75" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="2.125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="19.125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="2.125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="16.75" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="17.125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="18.875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="16" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="8" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="11.625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="7.125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="15.875" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="9.625" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="8.125" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="17.125" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="7.125" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="16.625" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="11" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="8" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="11.625" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="7.125" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="11" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="7.625" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="14.875" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="7.125" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="15.125" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="9.625" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="8" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="11.625" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="7.125" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="17.25" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="13.75" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="13.125" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="16" bestFit="1" customWidth="1"/>
+    <col min="57" max="57" width="7.125" bestFit="1" customWidth="1"/>
+    <col min="59" max="59" width="18" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="8.75" bestFit="1" customWidth="1"/>
+    <col min="61" max="61" width="5" bestFit="1" customWidth="1"/>
+    <col min="62" max="62" width="11.625" bestFit="1" customWidth="1"/>
+    <col min="63" max="63" width="7.125" bestFit="1" customWidth="1"/>
+    <col min="68" max="68" width="13" bestFit="1" customWidth="1"/>
+    <col min="70" max="70" width="7.5" bestFit="1" customWidth="1"/>
+    <col min="71" max="71" width="7.125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:57" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="3" spans="2:57" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="D3" s="7"/>
+      <c r="E3" s="8"/>
+      <c r="G3" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="I3" s="7"/>
+      <c r="J3" s="8"/>
+    </row>
+    <row r="4" spans="2:57" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="G4" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="J4" s="10" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="5" spans="2:57" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="J5" s="10" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="6" spans="2:57" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B6" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="G6" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="H6" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="I6" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="J6" s="13"/>
+    </row>
+    <row r="7" spans="2:57" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B7" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="F7" s="14"/>
+    </row>
+    <row r="8" spans="2:57" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E8" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="H8" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="I8" s="7"/>
+      <c r="J8" s="8"/>
+    </row>
+    <row r="9" spans="2:57" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E9" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="G9" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="J9" s="10" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="10" spans="2:57" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E10" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="G10" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="J10" s="10" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="11" spans="2:57" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E11" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="G11" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="J11" s="10" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="12" spans="2:57" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E12" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="G12" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="J12" s="10"/>
+    </row>
+    <row r="13" spans="2:57" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E13" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="G13" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="J13" s="10"/>
+    </row>
+    <row r="14" spans="2:57" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B14" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="C14" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="D14" s="12" t="s">
+        <v>138</v>
+      </c>
+      <c r="E14" s="13"/>
+      <c r="G14" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="J14" s="10" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="15" spans="2:57" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="G15" s="11" t="s">
+        <v>141</v>
+      </c>
+      <c r="H15" s="12" t="s">
+        <v>142</v>
+      </c>
+      <c r="I15" s="12" t="s">
+        <v>132</v>
+      </c>
+      <c r="J15" s="13"/>
+    </row>
+    <row r="16" spans="2:57" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B16" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="D16" s="7"/>
+      <c r="E16" s="8"/>
+    </row>
+    <row r="17" spans="2:10" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B17" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="E17" s="10" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="18" spans="2:10" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B18" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="E18" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="G18" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="H18" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="I18" s="7"/>
+      <c r="J18" s="8"/>
+    </row>
+    <row r="19" spans="2:10" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B19" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="C19" s="12" t="s">
+        <v>109</v>
+      </c>
+      <c r="D19" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="E19" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="G19" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="J19" s="10" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="20" spans="2:10" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="F20" s="15"/>
+      <c r="G20" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="J20" s="10" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="21" spans="2:10" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="G21" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="J21" s="10" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="22" spans="2:10" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B22" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="D22" s="7"/>
+      <c r="E22" s="8"/>
+      <c r="G22" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="J22" s="10"/>
+    </row>
+    <row r="23" spans="2:10" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B23" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="E23" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="G23" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="J23" s="10" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="24" spans="2:10" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B24" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="E24" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="G24" s="11" t="s">
+        <v>139</v>
+      </c>
+      <c r="H24" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="I24" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="J24" s="13" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="25" spans="2:10" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B25" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="E25" s="10" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="26" spans="2:10" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B26" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E26" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="G26" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="H26" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="I26" s="16"/>
+      <c r="J26" s="17"/>
+    </row>
+    <row r="27" spans="2:10" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B27" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E27" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="G27" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="J27" s="10" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="28" spans="2:10" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B28" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E28" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="G28" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="I28" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="J28" s="10" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="29" spans="2:10" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B29" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E29" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="G29" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="I29" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="J29" s="10"/>
+    </row>
+    <row r="30" spans="2:10" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B30" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="C30" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="D30" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="E30" s="13"/>
+      <c r="G30" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="I30" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="J30" s="10"/>
+    </row>
+    <row r="31" spans="2:10" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="F31" s="15"/>
+      <c r="G31" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="I31" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="J31" s="10"/>
+    </row>
+    <row r="32" spans="2:10" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B32" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="C32" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="D32" s="7"/>
+      <c r="E32" s="8"/>
+      <c r="G32" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="I32" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="J32" s="10"/>
+    </row>
+    <row r="33" spans="2:10" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B33" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="E33" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="G33" s="11" t="s">
+        <v>165</v>
+      </c>
+      <c r="H33" s="12" t="s">
+        <v>166</v>
+      </c>
+      <c r="I33" s="12" t="s">
+        <v>132</v>
+      </c>
+      <c r="J33" s="13" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="34" spans="2:10" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B34" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="E34" s="10" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="35" spans="2:10" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B35" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="E35" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="G35" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H35" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="I35" s="7"/>
+      <c r="J35" s="8"/>
+    </row>
+    <row r="36" spans="2:10" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B36" s="11" t="s">
+        <v>170</v>
+      </c>
+      <c r="C36" s="12" t="s">
+        <v>171</v>
+      </c>
+      <c r="D36" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="E36" s="13"/>
+      <c r="G36" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="H36" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="I36" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="J36" s="10" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="37" spans="2:10" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="G37" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="H37" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="I37" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="J37" s="10" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="38" spans="2:10" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="G38" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="H38" s="12" t="s">
+        <v>172</v>
+      </c>
+      <c r="I38" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="J38" s="13" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="39" spans="2:10" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B39" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C39" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="D39" s="7"/>
+      <c r="E39" s="8"/>
+    </row>
+    <row r="40" spans="2:10" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B40" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="E40" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="G40" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="H40" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="I40" s="7"/>
+      <c r="J40" s="8"/>
+    </row>
+    <row r="41" spans="2:10" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B41" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="E41" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="G41" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="H41" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="I41" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="J41" s="10" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="42" spans="2:10" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B42" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E42" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="G42" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="H42" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="I42" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="J42" s="10" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="43" spans="2:10" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B43" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="E43" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="G43" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="H43" s="12" t="s">
+        <v>172</v>
+      </c>
+      <c r="I43" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="J43" s="13" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="44" spans="2:10" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B44" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="E44" s="10" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="45" spans="2:10" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B45" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="E45" s="10"/>
+    </row>
+    <row r="46" spans="2:10" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B46" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="E46" s="10" t="s">
+        <v>167</v>
+      </c>
+      <c r="G46" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="H46" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="I46" s="7"/>
+      <c r="J46" s="8"/>
+    </row>
+    <row r="47" spans="2:10" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B47" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="C47" s="12" t="s">
+        <v>182</v>
+      </c>
+      <c r="D47" s="12" t="s">
+        <v>135</v>
+      </c>
+      <c r="E47" s="13"/>
+      <c r="G47" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="H47" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="I47" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="J47" s="10" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="48" spans="2:10" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="G48" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H48" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="I48" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="J48" s="10" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="49" spans="2:10" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B49" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C49" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="D49" s="7"/>
+      <c r="E49" s="8"/>
+      <c r="G49" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="H49" s="12" t="s">
+        <v>184</v>
+      </c>
+      <c r="I49" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="J49" s="13" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="50" spans="2:10" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B50" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="E50" s="10" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="51" spans="2:10" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B51" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="E51" s="10" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="52" spans="2:10" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B52" s="9" t="s">
+        <v>187</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="E52" s="10" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="53" spans="2:10" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B53" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="E53" s="10" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="54" spans="2:10" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B54" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="C54" s="12" t="s">
+        <v>188</v>
+      </c>
+      <c r="D54" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="E54" s="13"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/3_작업영역/0_테이블/테이블.xlsx
+++ b/3_작업영역/0_테이블/테이블.xlsx
@@ -1,18 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{BC93BC09-B44B-4D61-890B-39D903D607B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\awsintel4\aws4intelrepogitory\K_dessert\3_작업영역\0_테이블\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{245638A5-1D1A-4174-8A34-E2FE44B2E5FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13845" yWindow="1455" windowWidth="15540" windowHeight="16500" activeTab="1" xr2:uid="{89506D57-ACF2-4766-BACF-4F8058B8758D}"/>
+    <workbookView xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{89506D57-ACF2-4766-BACF-4F8058B8758D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
-  <oleSize ref="A1:U30"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -22,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="438" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="434" uniqueCount="187">
   <si>
     <t>index</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -539,10 +543,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>상세주소</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>M_ADDRESS_SEC</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -551,10 +551,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>VARCHAR2(200)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>DEFAULT SYSDATE</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -647,10 +643,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>주소_상세</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>다과 인덱스</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -763,19 +755,22 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>장바구니 인덱스</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>B_INDEX</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>회원 인덱스</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>B_STOCK</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>VARCHAR2(255)</t>
+  </si>
+  <si>
+    <t>D_OPEN</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>상세 주소</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -800,12 +795,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="15">
@@ -1015,25 +1016,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1">
@@ -1057,10 +1040,28 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1394,16 +1395,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -1475,7 +1476,7 @@
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="1" t="s">
         <v>36</v>
       </c>
       <c r="B5" s="1" t="s">
@@ -1491,15 +1492,6 @@
         <v>63</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="4"/>
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
-    </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>7</v>
@@ -1525,7 +1517,7 @@
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="1" t="s">
         <v>40</v>
       </c>
       <c r="B11" s="1" t="s">
@@ -1548,7 +1540,7 @@
       <c r="A14" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="1" t="s">
         <v>70</v>
       </c>
       <c r="C14" s="1" t="s">
@@ -1557,10 +1549,10 @@
       <c r="D14" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="E14" s="2" t="s">
+      <c r="E14" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="F14" s="2" t="s">
+      <c r="F14" s="1" t="s">
         <v>94</v>
       </c>
     </row>
@@ -1577,10 +1569,10 @@
       <c r="D15" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E15" s="2" t="s">
+      <c r="E15" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="F15" s="2" t="s">
+      <c r="F15" s="1" t="s">
         <v>95</v>
       </c>
     </row>
@@ -1605,7 +1597,7 @@
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="2" t="s">
+      <c r="A17" s="1" t="s">
         <v>36</v>
       </c>
       <c r="B17" s="1"/>
@@ -1616,11 +1608,6 @@
       <c r="E17" s="1"/>
       <c r="F17" s="1"/>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="3"/>
-      <c r="B18" s="3"/>
-      <c r="C18" s="3"/>
-    </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>43</v>
@@ -1628,7 +1615,6 @@
       <c r="B19" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="C19" s="3"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
@@ -1637,7 +1623,6 @@
       <c r="B20" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C20" s="3"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
@@ -1646,21 +1631,14 @@
       <c r="B21" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C21" s="3"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="2" t="s">
+      <c r="A22" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="B22" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C22" s="3"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="4"/>
-      <c r="B23" s="4"/>
-      <c r="C23" s="3"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
@@ -1686,7 +1664,7 @@
       <c r="D26" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E26" s="2" t="s">
+      <c r="E26" s="1" t="s">
         <v>97</v>
       </c>
     </row>
@@ -1700,21 +1678,21 @@
       <c r="C27" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D27" s="2" t="s">
+      <c r="D27" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="E27" s="2" t="s">
+      <c r="E27" s="1" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" s="2" t="s">
+      <c r="A28" s="1" t="s">
         <v>36</v>
       </c>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
       <c r="D28" s="1"/>
-      <c r="E28" s="2"/>
+      <c r="E28" s="1"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
@@ -1741,7 +1719,7 @@
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" s="2" t="s">
+      <c r="A33" s="1" t="s">
         <v>40</v>
       </c>
       <c r="B33" s="1" t="s">
@@ -1781,7 +1759,7 @@
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A39" s="2" t="s">
+      <c r="A39" s="1" t="s">
         <v>36</v>
       </c>
       <c r="B39" s="1" t="s">
@@ -1819,7 +1797,7 @@
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A46" s="2" t="s">
+      <c r="A46" s="1" t="s">
         <v>40</v>
       </c>
       <c r="B46" s="1"/>
@@ -1846,13 +1824,13 @@
       <c r="C49" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D49" s="2" t="s">
+      <c r="D49" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E49" s="2" t="s">
+      <c r="E49" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="F49" s="2" t="s">
+      <c r="F49" s="1" t="s">
         <v>28</v>
       </c>
     </row>
@@ -1866,13 +1844,13 @@
       <c r="C50" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D50" s="2" t="s">
+      <c r="D50" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="E50" s="2" t="s">
+      <c r="E50" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="F50" s="2" t="s">
+      <c r="F50" s="1" t="s">
         <v>56</v>
       </c>
     </row>
@@ -1884,14 +1862,14 @@
         <v>81</v>
       </c>
       <c r="C51" s="1"/>
-      <c r="D51" s="2"/>
+      <c r="D51" s="1"/>
       <c r="E51" s="1" t="s">
         <v>81</v>
       </c>
       <c r="F51" s="1"/>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A52" s="2" t="s">
+      <c r="A52" s="1" t="s">
         <v>36</v>
       </c>
       <c r="B52" s="1"/>
@@ -1913,7 +1891,7 @@
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A55" s="2" t="s">
+      <c r="A55" s="1" t="s">
         <v>60</v>
       </c>
       <c r="B55" s="1" t="s">
@@ -1929,7 +1907,7 @@
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A57" s="2" t="s">
+      <c r="A57" s="1" t="s">
         <v>40</v>
       </c>
       <c r="B57" s="1" t="s">
@@ -1973,7 +1951,7 @@
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A65" s="2" t="s">
+      <c r="A65" s="1" t="s">
         <v>36</v>
       </c>
       <c r="B65" s="1" t="s">
@@ -1991,7 +1969,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87580854-C28E-4E95-AB15-75B01A5EA365}">
-  <dimension ref="B2:BE54"/>
+  <dimension ref="B2:J53"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3.25" customWidth="1"/>
@@ -2050,54 +2028,54 @@
     <col min="71" max="71" width="7.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:57" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="3" spans="2:57" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="6" t="s">
+    <row r="2" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="3" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B3" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="D3" s="7"/>
-      <c r="E3" s="8"/>
-      <c r="G3" s="6" t="s">
+      <c r="D3" s="11"/>
+      <c r="E3" s="12"/>
+      <c r="G3" s="10" t="s">
         <v>104</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="H3" s="11" t="s">
         <v>105</v>
       </c>
-      <c r="I3" s="7"/>
-      <c r="J3" s="8"/>
-    </row>
-    <row r="4" spans="2:57" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="9" t="s">
+      <c r="I3" s="11"/>
+      <c r="J3" s="12"/>
+    </row>
+    <row r="4" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B4" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="14" t="s">
         <v>106</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" s="14" t="s">
         <v>107</v>
       </c>
-      <c r="E4" s="10" t="s">
+      <c r="E4" s="15" t="s">
         <v>108</v>
       </c>
-      <c r="G4" s="9" t="s">
+      <c r="G4" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="H4" s="14" t="s">
         <v>106</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="I4" s="14" t="s">
         <v>107</v>
       </c>
-      <c r="J4" s="10" t="s">
+      <c r="J4" s="15" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="5" spans="2:57" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="9" t="s">
-        <v>31</v>
+    <row r="5" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B5" s="3" t="s">
+        <v>182</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>109</v>
@@ -2105,10 +2083,10 @@
       <c r="D5" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="E5" s="10" t="s">
+      <c r="E5" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="G5" s="9" t="s">
+      <c r="G5" s="3" t="s">
         <v>111</v>
       </c>
       <c r="H5" s="1" t="s">
@@ -2117,12 +2095,12 @@
       <c r="I5" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="J5" s="10" t="s">
+      <c r="J5" s="4" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="6" spans="2:57" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="9" t="s">
+    <row r="6" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B6" s="3" t="s">
         <v>68</v>
       </c>
       <c r="C6" s="1" t="s">
@@ -2131,22 +2109,22 @@
       <c r="D6" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="E6" s="10" t="s">
+      <c r="E6" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="G6" s="11" t="s">
+      <c r="G6" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="H6" s="12" t="s">
+      <c r="H6" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="I6" s="12" t="s">
+      <c r="I6" s="6" t="s">
         <v>117</v>
       </c>
-      <c r="J6" s="13"/>
-    </row>
-    <row r="7" spans="2:57" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B7" s="9" t="s">
+      <c r="J6" s="7"/>
+    </row>
+    <row r="7" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B7" s="3" t="s">
         <v>62</v>
       </c>
       <c r="C7" s="1" t="s">
@@ -2155,13 +2133,13 @@
       <c r="D7" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="E7" s="10" t="s">
+      <c r="E7" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="F7" s="14"/>
-    </row>
-    <row r="8" spans="2:57" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="9" t="s">
+      <c r="F7" s="8"/>
+    </row>
+    <row r="8" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B8" s="3" t="s">
         <v>32</v>
       </c>
       <c r="C8" s="1" t="s">
@@ -2170,20 +2148,20 @@
       <c r="D8" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="E8" s="10" t="s">
+      <c r="E8" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="G8" s="6" t="s">
+      <c r="G8" s="10" t="s">
         <v>120</v>
       </c>
-      <c r="H8" s="7" t="s">
+      <c r="H8" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="I8" s="7"/>
-      <c r="J8" s="8"/>
-    </row>
-    <row r="9" spans="2:57" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="9" t="s">
+      <c r="I8" s="11"/>
+      <c r="J8" s="12"/>
+    </row>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B9" s="3" t="s">
         <v>33</v>
       </c>
       <c r="C9" s="1" t="s">
@@ -2192,24 +2170,24 @@
       <c r="D9" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="E9" s="10" t="s">
+      <c r="E9" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="G9" s="9" t="s">
+      <c r="G9" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="H9" s="1" t="s">
+      <c r="H9" s="14" t="s">
         <v>106</v>
       </c>
-      <c r="I9" s="1" t="s">
+      <c r="I9" s="14" t="s">
         <v>107</v>
       </c>
-      <c r="J9" s="10" t="s">
+      <c r="J9" s="15" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="10" spans="2:57" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="9" t="s">
+    <row r="10" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B10" s="3" t="s">
         <v>34</v>
       </c>
       <c r="C10" s="1" t="s">
@@ -2218,10 +2196,10 @@
       <c r="D10" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="E10" s="10" t="s">
+      <c r="E10" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="G10" s="9" t="s">
+      <c r="G10" s="3" t="s">
         <v>124</v>
       </c>
       <c r="H10" s="1" t="s">
@@ -2230,12 +2208,12 @@
       <c r="I10" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="J10" s="10" t="s">
+      <c r="J10" s="4" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="11" spans="2:57" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="9" t="s">
+    <row r="11" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B11" s="3" t="s">
         <v>126</v>
       </c>
       <c r="C11" s="1" t="s">
@@ -2244,48 +2222,48 @@
       <c r="D11" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="E11" s="10" t="s">
+      <c r="E11" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="G11" s="9" t="s">
+      <c r="G11" s="3" t="s">
         <v>65</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J11" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="J11" s="4" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="12" spans="2:57" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="9" t="s">
+    <row r="12" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B12" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="C12" s="1" t="s">
         <v>129</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>130</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="E12" s="10" t="s">
+      <c r="E12" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="G12" s="9" t="s">
+      <c r="G12" s="3" t="s">
         <v>66</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="J12" s="10"/>
-    </row>
-    <row r="13" spans="2:57" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="J12" s="4"/>
+    </row>
+    <row r="13" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B13" s="3" t="s">
         <v>35</v>
       </c>
       <c r="C13" s="1" t="s">
@@ -2294,231 +2272,231 @@
       <c r="D13" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="E13" s="10" t="s">
+      <c r="E13" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="I13" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="G13" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="H13" s="1" t="s">
+      <c r="J13" s="4"/>
+    </row>
+    <row r="14" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B14" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="I13" s="1" t="s">
+      <c r="C14" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="J13" s="10"/>
-    </row>
-    <row r="14" spans="2:57" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="11" t="s">
+      <c r="D14" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="C14" s="12" t="s">
+      <c r="E14" s="7"/>
+      <c r="G14" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="D14" s="12" t="s">
+      <c r="H14" s="1" t="s">
         <v>138</v>
-      </c>
-      <c r="E14" s="13"/>
-      <c r="G14" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="H14" s="1" t="s">
-        <v>140</v>
       </c>
       <c r="I14" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="J14" s="10" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="15" spans="2:57" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="G15" s="11" t="s">
+      <c r="J14" s="4" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="15" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="G15" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="H15" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="I15" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="J15" s="7"/>
+    </row>
+    <row r="16" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B16" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" s="11" t="s">
         <v>141</v>
       </c>
-      <c r="H15" s="12" t="s">
+      <c r="D16" s="11"/>
+      <c r="E16" s="12"/>
+    </row>
+    <row r="17" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B17" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="C17" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="D17" s="14" t="s">
+        <v>107</v>
+      </c>
+      <c r="E17" s="15" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="18" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B18" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C18" s="1" t="s">
         <v>142</v>
-      </c>
-      <c r="I15" s="12" t="s">
-        <v>132</v>
-      </c>
-      <c r="J15" s="13"/>
-    </row>
-    <row r="16" spans="2:57" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="D16" s="7"/>
-      <c r="E16" s="8"/>
-    </row>
-    <row r="17" spans="2:10" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B17" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="E17" s="10" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="18" spans="2:10" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>144</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="E18" s="10" t="s">
+      <c r="E18" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="G18" s="6" t="s">
+      <c r="G18" s="10" t="s">
+        <v>143</v>
+      </c>
+      <c r="H18" s="11" t="s">
+        <v>144</v>
+      </c>
+      <c r="I18" s="11"/>
+      <c r="J18" s="12"/>
+    </row>
+    <row r="19" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B19" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="G19" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="H19" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="I19" s="14" t="s">
+        <v>107</v>
+      </c>
+      <c r="J19" s="15" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="20" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="F20" s="9"/>
+      <c r="G20" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="H20" s="1" t="s">
         <v>145</v>
-      </c>
-      <c r="H18" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="I18" s="7"/>
-      <c r="J18" s="8"/>
-    </row>
-    <row r="19" spans="2:10" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B19" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="C19" s="12" t="s">
-        <v>109</v>
-      </c>
-      <c r="D19" s="12" t="s">
-        <v>80</v>
-      </c>
-      <c r="E19" s="13" t="s">
-        <v>128</v>
-      </c>
-      <c r="G19" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="H19" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="I19" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="J19" s="10" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="20" spans="2:10" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="F20" s="15"/>
-      <c r="G20" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="H20" s="1" t="s">
-        <v>147</v>
       </c>
       <c r="I20" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="J20" s="10" t="s">
+      <c r="J20" s="4" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="21" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="G21" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="J21" s="4" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="22" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B22" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="C22" s="11" t="s">
+        <v>147</v>
+      </c>
+      <c r="D22" s="11"/>
+      <c r="E22" s="12"/>
+      <c r="G22" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="H22" s="1" t="s">
         <v>148</v>
-      </c>
-    </row>
-    <row r="21" spans="2:10" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="G21" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="H21" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="I21" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J21" s="10" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="22" spans="2:10" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C22" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="D22" s="7"/>
-      <c r="E22" s="8"/>
-      <c r="G22" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="H22" s="1" t="s">
-        <v>150</v>
       </c>
       <c r="I22" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="J22" s="10"/>
-    </row>
-    <row r="23" spans="2:10" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B23" s="9" t="s">
+      <c r="J22" s="4"/>
+    </row>
+    <row r="23" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B23" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="C23" s="1" t="s">
+      <c r="C23" s="14" t="s">
         <v>106</v>
       </c>
-      <c r="D23" s="1" t="s">
+      <c r="D23" s="14" t="s">
         <v>107</v>
       </c>
-      <c r="E23" s="10" t="s">
+      <c r="E23" s="15" t="s">
         <v>108</v>
       </c>
-      <c r="G23" s="9" t="s">
+      <c r="G23" s="3" t="s">
         <v>124</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="I23" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="J23" s="10" t="s">
+      <c r="J23" s="4" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="24" spans="2:10" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B24" s="9" t="s">
+    <row r="24" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B24" s="3" t="s">
         <v>37</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="E24" s="10" t="s">
+      <c r="E24" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="G24" s="11" t="s">
-        <v>139</v>
-      </c>
-      <c r="H24" s="12" t="s">
-        <v>152</v>
-      </c>
-      <c r="I24" s="12" t="s">
+      <c r="G24" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="H24" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="I24" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="J24" s="13" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="25" spans="2:10" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B25" s="9" t="s">
+      <c r="J24" s="7" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="25" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B25" s="3" t="s">
         <v>70</v>
       </c>
       <c r="C25" s="1" t="s">
@@ -2527,34 +2505,34 @@
       <c r="D25" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="E25" s="10" t="s">
+      <c r="E25" s="4" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="26" spans="2:10" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B26" s="9" t="s">
+    <row r="26" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B26" s="3" t="s">
         <v>41</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="E26" s="10" t="s">
-        <v>133</v>
-      </c>
-      <c r="G26" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="H26" s="7" t="s">
-        <v>155</v>
+      <c r="E26" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="G26" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="H26" s="11" t="s">
+        <v>153</v>
       </c>
       <c r="I26" s="16"/>
       <c r="J26" s="17"/>
     </row>
-    <row r="27" spans="2:10" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B27" s="9" t="s">
+    <row r="27" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B27" s="3" t="s">
         <v>126</v>
       </c>
       <c r="C27" s="1" t="s">
@@ -2563,50 +2541,50 @@
       <c r="D27" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="E27" s="10" t="s">
+      <c r="E27" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="G27" s="9" t="s">
+      <c r="G27" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="H27" s="1" t="s">
+      <c r="H27" s="14" t="s">
         <v>106</v>
       </c>
-      <c r="I27" s="1" t="s">
+      <c r="I27" s="14" t="s">
         <v>107</v>
       </c>
-      <c r="J27" s="10" t="s">
+      <c r="J27" s="15" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="28" spans="2:10" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B28" s="9" t="s">
-        <v>156</v>
+    <row r="28" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B28" s="3" t="s">
+        <v>186</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="E28" s="10" t="s">
+      <c r="E28" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="G28" s="9" t="s">
-        <v>157</v>
+      <c r="G28" s="3" t="s">
+        <v>154</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="I28" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="J28" s="10" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="29" spans="2:10" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B29" s="9" t="s">
+      <c r="J28" s="4" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="29" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B29" s="3" t="s">
         <v>92</v>
       </c>
       <c r="C29" s="1" t="s">
@@ -2615,474 +2593,460 @@
       <c r="D29" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="E29" s="10" t="s">
+      <c r="E29" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="G29" s="9" t="s">
+      <c r="G29" s="3" t="s">
         <v>32</v>
       </c>
       <c r="H29" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="I29" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="J29" s="4"/>
+    </row>
+    <row r="30" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B30" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="E30" s="7"/>
+      <c r="G30" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="I30" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="J30" s="4"/>
+    </row>
+    <row r="31" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="F31" s="9"/>
+      <c r="G31" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H31" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="I29" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="J29" s="10"/>
-    </row>
-    <row r="30" spans="2:10" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B30" s="11" t="s">
-        <v>94</v>
-      </c>
-      <c r="C30" s="12" t="s">
+      <c r="I31" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="J31" s="4"/>
+    </row>
+    <row r="32" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B32" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="C32" s="11" t="s">
         <v>160</v>
       </c>
-      <c r="D30" s="12" t="s">
-        <v>96</v>
-      </c>
-      <c r="E30" s="13"/>
-      <c r="G30" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="H30" s="1" t="s">
+      <c r="D32" s="11"/>
+      <c r="E32" s="12"/>
+      <c r="G32" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H32" s="1" t="s">
         <v>161</v>
-      </c>
-      <c r="I30" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="J30" s="10"/>
-    </row>
-    <row r="31" spans="2:10" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="F31" s="15"/>
-      <c r="G31" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="H31" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="I31" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="J31" s="10"/>
-    </row>
-    <row r="32" spans="2:10" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B32" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="C32" s="7" t="s">
-        <v>163</v>
-      </c>
-      <c r="D32" s="7"/>
-      <c r="E32" s="8"/>
-      <c r="G32" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="H32" s="1" t="s">
-        <v>164</v>
       </c>
       <c r="I32" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="J32" s="10"/>
-    </row>
-    <row r="33" spans="2:10" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B33" s="9" t="s">
+      <c r="J32" s="4"/>
+    </row>
+    <row r="33" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B33" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="C33" s="1" t="s">
+      <c r="C33" s="14" t="s">
         <v>106</v>
       </c>
-      <c r="D33" s="1" t="s">
+      <c r="D33" s="14" t="s">
         <v>107</v>
       </c>
-      <c r="E33" s="10" t="s">
+      <c r="E33" s="15" t="s">
         <v>108</v>
       </c>
-      <c r="G33" s="11" t="s">
-        <v>165</v>
-      </c>
-      <c r="H33" s="12" t="s">
-        <v>166</v>
-      </c>
-      <c r="I33" s="12" t="s">
-        <v>132</v>
-      </c>
-      <c r="J33" s="13" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="34" spans="2:10" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B34" s="9" t="s">
+      <c r="G33" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="H33" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="I33" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="J33" s="7" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="34" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B34" s="3" t="s">
         <v>37</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D34" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="E34" s="10" t="s">
+      <c r="E34" s="4" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="35" spans="2:10" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="9" t="s">
+    <row r="35" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B35" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="D35" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="E35" s="10" t="s">
+      <c r="E35" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="G35" s="6" t="s">
+      <c r="G35" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="H35" s="7" t="s">
-        <v>169</v>
-      </c>
-      <c r="I35" s="7"/>
-      <c r="J35" s="8"/>
-    </row>
-    <row r="36" spans="2:10" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B36" s="11" t="s">
-        <v>170</v>
-      </c>
-      <c r="C36" s="12" t="s">
-        <v>171</v>
-      </c>
-      <c r="D36" s="12" t="s">
+      <c r="H35" s="11" t="s">
+        <v>166</v>
+      </c>
+      <c r="I35" s="11"/>
+      <c r="J35" s="12"/>
+    </row>
+    <row r="36" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B36" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="C36" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="D36" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="E36" s="13"/>
-      <c r="G36" s="9" t="s">
+      <c r="E36" s="7"/>
+      <c r="G36" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="H36" s="1" t="s">
+      <c r="H36" s="14" t="s">
         <v>106</v>
       </c>
-      <c r="I36" s="1" t="s">
+      <c r="I36" s="14" t="s">
         <v>107</v>
       </c>
-      <c r="J36" s="10" t="s">
+      <c r="J36" s="15" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="37" spans="2:10" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="G37" s="9" t="s">
+    <row r="37" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="G37" s="3" t="s">
         <v>60</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="I37" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="J37" s="10" t="s">
+      <c r="J37" s="4" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="38" spans="2:10" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="G38" s="11" t="s">
+    <row r="38" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="G38" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="H38" s="12" t="s">
-        <v>172</v>
-      </c>
-      <c r="I38" s="12" t="s">
+      <c r="H38" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="I38" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="J38" s="13" t="s">
+      <c r="J38" s="7" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="39" spans="2:10" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B39" s="6" t="s">
+    <row r="39" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B39" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="C39" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="D39" s="7"/>
-      <c r="E39" s="8"/>
-    </row>
-    <row r="40" spans="2:10" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B40" s="9" t="s">
+      <c r="C39" s="11" t="s">
+        <v>170</v>
+      </c>
+      <c r="D39" s="11"/>
+      <c r="E39" s="12"/>
+    </row>
+    <row r="40" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B40" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="C40" s="1" t="s">
+      <c r="C40" s="14" t="s">
         <v>106</v>
       </c>
-      <c r="D40" s="1" t="s">
+      <c r="D40" s="14" t="s">
         <v>107</v>
       </c>
-      <c r="E40" s="10" t="s">
+      <c r="E40" s="15" t="s">
         <v>108</v>
       </c>
-      <c r="G40" s="6" t="s">
+      <c r="G40" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="H40" s="7" t="s">
-        <v>174</v>
-      </c>
-      <c r="I40" s="7"/>
-      <c r="J40" s="8"/>
-    </row>
-    <row r="41" spans="2:10" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B41" s="9" t="s">
+      <c r="H40" s="11" t="s">
+        <v>171</v>
+      </c>
+      <c r="I40" s="11"/>
+      <c r="J40" s="12"/>
+    </row>
+    <row r="41" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B41" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="D41" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="E41" s="10" t="s">
+      <c r="E41" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="G41" s="9" t="s">
+      <c r="G41" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="H41" s="1" t="s">
+      <c r="H41" s="14" t="s">
         <v>106</v>
       </c>
-      <c r="I41" s="1" t="s">
+      <c r="I41" s="14" t="s">
         <v>107</v>
       </c>
-      <c r="J41" s="10" t="s">
+      <c r="J41" s="15" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="42" spans="2:10" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B42" s="9" t="s">
+    <row r="42" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B42" s="3" t="s">
         <v>46</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="D42" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="E42" s="10" t="s">
+      <c r="E42" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="G42" s="9" t="s">
+      <c r="G42" s="3" t="s">
         <v>42</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="I42" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="J42" s="10" t="s">
+      <c r="J42" s="4" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="43" spans="2:10" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B43" s="9" t="s">
+    <row r="43" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B43" s="3" t="s">
         <v>47</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="D43" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="E43" s="10" t="s">
+      <c r="E43" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="G43" s="11" t="s">
+      <c r="G43" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="H43" s="12" t="s">
-        <v>172</v>
-      </c>
-      <c r="I43" s="12" t="s">
+      <c r="H43" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="I43" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="J43" s="13" t="s">
+      <c r="J43" s="7" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="44" spans="2:10" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B44" s="9" t="s">
+    <row r="44" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B44" s="3" t="s">
         <v>48</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="D44" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="E44" s="10" t="s">
+      <c r="E44" s="4" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="45" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B45" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="E45" s="4"/>
+    </row>
+    <row r="46" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B46" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="E46" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="G46" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="H46" s="11" t="s">
+        <v>177</v>
+      </c>
+      <c r="I46" s="11"/>
+      <c r="J46" s="12"/>
+    </row>
+    <row r="47" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B47" s="5" t="s">
         <v>178</v>
       </c>
-    </row>
-    <row r="45" spans="2:10" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B45" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="C45" s="1" t="s">
+      <c r="C47" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="D45" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="E45" s="10"/>
-    </row>
-    <row r="46" spans="2:10" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B46" s="9" t="s">
-        <v>165</v>
-      </c>
-      <c r="C46" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="D46" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="E46" s="10" t="s">
-        <v>167</v>
-      </c>
-      <c r="G46" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="H46" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="I46" s="7"/>
-      <c r="J46" s="8"/>
-    </row>
-    <row r="47" spans="2:10" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B47" s="11" t="s">
-        <v>181</v>
-      </c>
-      <c r="C47" s="12" t="s">
-        <v>182</v>
-      </c>
-      <c r="D47" s="12" t="s">
-        <v>135</v>
-      </c>
-      <c r="E47" s="13"/>
-      <c r="G47" s="9" t="s">
+      <c r="D47" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="E47" s="7"/>
+      <c r="G47" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="H47" s="1" t="s">
+      <c r="H47" s="14" t="s">
         <v>106</v>
       </c>
-      <c r="I47" s="1" t="s">
+      <c r="I47" s="14" t="s">
         <v>107</v>
       </c>
-      <c r="J47" s="10" t="s">
+      <c r="J47" s="15" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="48" spans="2:10" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="G48" s="9" t="s">
+    <row r="48" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="G48" s="3" t="s">
         <v>50</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="I48" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="J48" s="10" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="49" spans="2:10" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B49" s="6" t="s">
+      <c r="J48" s="4" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="49" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B49" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="C49" s="7" t="s">
-        <v>183</v>
-      </c>
-      <c r="D49" s="7"/>
-      <c r="E49" s="8"/>
-      <c r="G49" s="11" t="s">
+      <c r="C49" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="D49" s="11"/>
+      <c r="E49" s="12"/>
+      <c r="G49" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="H49" s="12" t="s">
-        <v>184</v>
-      </c>
-      <c r="I49" s="12" t="s">
+      <c r="H49" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="I49" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="J49" s="13" t="s">
+      <c r="J49" s="7" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="50" spans="2:10" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B50" s="9" t="s">
+    <row r="50" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B50" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="C50" s="1" t="s">
+      <c r="C50" s="14" t="s">
         <v>106</v>
       </c>
-      <c r="D50" s="1" t="s">
+      <c r="D50" s="14" t="s">
         <v>107</v>
       </c>
-      <c r="E50" s="10" t="s">
+      <c r="E50" s="15" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="51" spans="2:10" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B51" s="9" t="s">
-        <v>185</v>
+    <row r="51" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B51" s="3" t="s">
+        <v>182</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>186</v>
+        <v>109</v>
       </c>
       <c r="D51" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="E51" s="10" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="52" spans="2:10" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B52" s="9" t="s">
-        <v>187</v>
+      <c r="E51" s="4" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="52" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B52" s="3" t="s">
+        <v>52</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>109</v>
+        <v>165</v>
       </c>
       <c r="D52" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="E52" s="10" t="s">
+      <c r="E52" s="4" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="53" spans="2:10" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B53" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="C53" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="D53" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="E53" s="10" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="54" spans="2:10" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B54" s="11" t="s">
+    <row r="53" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B53" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="C54" s="12" t="s">
-        <v>188</v>
-      </c>
-      <c r="D54" s="12" t="s">
+      <c r="C53" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="D53" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="E54" s="13"/>
+      <c r="E53" s="7"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/3_작업영역/0_테이블/테이블.xlsx
+++ b/3_작업영역/0_테이블/테이블.xlsx
@@ -1,32 +1,43 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\awsintel4\aws4intelrepogitory\K_dessert\3_작업영역\0_테이블\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Awsintel4 Repository\AwsIntel4_OWR\K_dessert\3_작업영역\0_테이블\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{245638A5-1D1A-4174-8A34-E2FE44B2E5FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DA36AED-25A1-47A1-B9B5-61EDBA9ED0D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{89506D57-ACF2-4766-BACF-4F8058B8758D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{89506D57-ACF2-4766-BACF-4F8058B8758D}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet2 (3)" sheetId="4" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId2"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId3"/>
+    <sheet name="Sheet2 (2)" sheetId="3" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="434" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1105" uniqueCount="204">
   <si>
     <t>index</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -772,6 +783,71 @@
   <si>
     <t>상세 주소</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>생년월일</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M_BIRTH</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>,</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>);</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NUMBER(1,0)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>공지여부(0:일반/1:공지)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>F_IMAGE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>주문상태 테이블</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>처리설명</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>STA_NOTICE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UNIQUE NOT NULL</t>
+  </si>
+  <si>
+    <t>조인테이블</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>태그 내용</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M_NOTE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CREATE TABLE MEMBER(</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FOREIGN KEY</t>
+  </si>
+  <si>
+    <t>CLOB</t>
   </si>
 </sst>
 </file>
@@ -795,7 +871,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -808,8 +884,32 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="15">
+  <borders count="18">
     <border>
       <left/>
       <right/>
@@ -1003,13 +1103,46 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1062,6 +1195,81 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="10" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="13" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="14" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1377,6 +1585,1287 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09F92FCC-166C-4E7D-84B0-227CCB7DD483}">
+  <dimension ref="B2:R53"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="3.25" customWidth="1"/>
+    <col min="2" max="2" width="22.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.75" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.25" customWidth="1"/>
+    <col min="7" max="7" width="2.125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="19.125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="2.125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7.125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="24.375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="17.125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="39.5" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="2.125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="17.125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="18.875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="16" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="8" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="11.625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="7.125" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="15.875" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="9.625" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="8.125" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="17.125" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="7.125" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="16.625" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="11" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="8" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="11.625" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="7.125" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="11" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="7.625" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="14.875" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="7.125" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="15.125" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="9.625" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="8" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="11.625" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="7.125" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="17.25" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="13.75" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="13.125" bestFit="1" customWidth="1"/>
+    <col min="57" max="57" width="16" bestFit="1" customWidth="1"/>
+    <col min="58" max="58" width="7.125" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="18" bestFit="1" customWidth="1"/>
+    <col min="61" max="61" width="8.75" bestFit="1" customWidth="1"/>
+    <col min="62" max="62" width="5" bestFit="1" customWidth="1"/>
+    <col min="63" max="63" width="11.625" bestFit="1" customWidth="1"/>
+    <col min="64" max="64" width="7.125" bestFit="1" customWidth="1"/>
+    <col min="69" max="69" width="13" bestFit="1" customWidth="1"/>
+    <col min="71" max="71" width="7.5" bestFit="1" customWidth="1"/>
+    <col min="72" max="72" width="7.125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:18" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="3" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B3" s="35" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="36" t="s">
+        <v>103</v>
+      </c>
+      <c r="D3" s="36"/>
+      <c r="E3" s="37"/>
+      <c r="H3" s="35" t="s">
+        <v>152</v>
+      </c>
+      <c r="I3" s="36" t="s">
+        <v>153</v>
+      </c>
+      <c r="J3" s="41"/>
+      <c r="K3" s="42"/>
+    </row>
+    <row r="4" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B4" s="38" t="s">
+        <v>55</v>
+      </c>
+      <c r="C4" s="39" t="s">
+        <v>106</v>
+      </c>
+      <c r="D4" s="39" t="s">
+        <v>107</v>
+      </c>
+      <c r="E4" s="40" t="s">
+        <v>108</v>
+      </c>
+      <c r="H4" s="38" t="s">
+        <v>55</v>
+      </c>
+      <c r="I4" s="39" t="s">
+        <v>106</v>
+      </c>
+      <c r="J4" s="39" t="s">
+        <v>107</v>
+      </c>
+      <c r="K4" s="40" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="5" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B5" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="E5" s="29" t="s">
+        <v>110</v>
+      </c>
+      <c r="F5" s="23"/>
+      <c r="H5" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="K5" s="29" t="s">
+        <v>110</v>
+      </c>
+      <c r="O5" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="6" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B6" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="E6" s="32" t="s">
+        <v>197</v>
+      </c>
+      <c r="F6" s="23"/>
+      <c r="H6" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="K6" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="O6" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="P6" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="Q6" s="29"/>
+      <c r="R6" s="23" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="7" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B7" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="F7" s="23"/>
+      <c r="H7" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="I7" s="34" t="s">
+        <v>158</v>
+      </c>
+      <c r="J7" s="34" t="s">
+        <v>203</v>
+      </c>
+      <c r="K7" s="4"/>
+      <c r="O7" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="P7" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q7" s="32" t="s">
+        <v>119</v>
+      </c>
+      <c r="R7" s="23" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="8" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B8" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="F8" s="23"/>
+      <c r="H8" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="J8" s="34" t="s">
+        <v>203</v>
+      </c>
+      <c r="K8" s="4"/>
+      <c r="O8" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="P8" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q8" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="R8" s="23" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="9" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B9" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="F9" s="23"/>
+      <c r="H9" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="K9" s="4"/>
+      <c r="O9" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="P9" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q9" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="R9" s="23" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="10" spans="2:18" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B10" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E10" s="32" t="s">
+        <v>197</v>
+      </c>
+      <c r="F10" s="23"/>
+      <c r="H10" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="I10" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="J10" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="K10" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="O10" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="P10" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q10" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="R10" s="23" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="11" spans="2:18" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B11" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="F11" s="23"/>
+      <c r="O11" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="P11" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q11" s="32" t="s">
+        <v>119</v>
+      </c>
+      <c r="R11" s="23" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="12" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B12" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="F12" s="23"/>
+      <c r="H12" s="35" t="s">
+        <v>27</v>
+      </c>
+      <c r="I12" s="36" t="s">
+        <v>166</v>
+      </c>
+      <c r="J12" s="36"/>
+      <c r="K12" s="37"/>
+      <c r="O12" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="P12" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q12" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="R12" s="23" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="13" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B13" s="25" t="s">
+        <v>187</v>
+      </c>
+      <c r="C13" s="24" t="s">
+        <v>188</v>
+      </c>
+      <c r="D13" s="24" t="s">
+        <v>83</v>
+      </c>
+      <c r="E13" s="26" t="s">
+        <v>119</v>
+      </c>
+      <c r="F13" s="23"/>
+      <c r="H13" s="38" t="s">
+        <v>55</v>
+      </c>
+      <c r="I13" s="39" t="s">
+        <v>106</v>
+      </c>
+      <c r="J13" s="39" t="s">
+        <v>107</v>
+      </c>
+      <c r="K13" s="40" t="s">
+        <v>108</v>
+      </c>
+      <c r="O13" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="P13" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q13" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="R13" s="23" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="14" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B14" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="F14" s="23"/>
+      <c r="H14" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="K14" s="30" t="s">
+        <v>202</v>
+      </c>
+      <c r="O14" s="24" t="s">
+        <v>188</v>
+      </c>
+      <c r="P14" s="24" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q14" s="26" t="s">
+        <v>119</v>
+      </c>
+      <c r="R14" s="23" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="15" spans="2:18" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B15" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="F15" s="23"/>
+      <c r="H15" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="I15" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="J15" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="K15" s="31" t="s">
+        <v>202</v>
+      </c>
+      <c r="O15" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="P15" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q15" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="R15" s="23" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="16" spans="2:18" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B16" s="27" t="s">
+        <v>108</v>
+      </c>
+      <c r="C16" s="28" t="s">
+        <v>200</v>
+      </c>
+      <c r="D16" s="28" t="s">
+        <v>96</v>
+      </c>
+      <c r="E16" s="7"/>
+      <c r="F16" s="23"/>
+      <c r="O16" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="P16" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="Q16" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="R16" s="23" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="17" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H17" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="I17" s="36" t="s">
+        <v>171</v>
+      </c>
+      <c r="J17" s="36"/>
+      <c r="K17" s="37"/>
+      <c r="O17" s="28" t="s">
+        <v>200</v>
+      </c>
+      <c r="P17" s="28" t="s">
+        <v>96</v>
+      </c>
+      <c r="Q17" s="7"/>
+    </row>
+    <row r="18" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B18" s="35" t="s">
+        <v>7</v>
+      </c>
+      <c r="C18" s="36" t="s">
+        <v>141</v>
+      </c>
+      <c r="D18" s="36" t="s">
+        <v>198</v>
+      </c>
+      <c r="E18" s="37"/>
+      <c r="H18" s="38" t="s">
+        <v>55</v>
+      </c>
+      <c r="I18" s="39" t="s">
+        <v>106</v>
+      </c>
+      <c r="J18" s="39" t="s">
+        <v>107</v>
+      </c>
+      <c r="K18" s="40" t="s">
+        <v>108</v>
+      </c>
+      <c r="O18" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="19" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B19" s="38" t="s">
+        <v>55</v>
+      </c>
+      <c r="C19" s="39" t="s">
+        <v>106</v>
+      </c>
+      <c r="D19" s="39" t="s">
+        <v>107</v>
+      </c>
+      <c r="E19" s="40" t="s">
+        <v>108</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="J19" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="K19" s="30" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="20" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B20" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="E20" s="30" t="s">
+        <v>202</v>
+      </c>
+      <c r="H20" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="I20" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="J20" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="K20" s="31" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="21" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B21" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="E21" s="31" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="22" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="23" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B23" s="35" t="s">
+        <v>6</v>
+      </c>
+      <c r="C23" s="36" t="s">
+        <v>147</v>
+      </c>
+      <c r="D23" s="36"/>
+      <c r="E23" s="37"/>
+      <c r="H23" s="35" t="s">
+        <v>14</v>
+      </c>
+      <c r="I23" s="36" t="s">
+        <v>177</v>
+      </c>
+      <c r="J23" s="36"/>
+      <c r="K23" s="37"/>
+    </row>
+    <row r="24" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B24" s="38" t="s">
+        <v>55</v>
+      </c>
+      <c r="C24" s="39" t="s">
+        <v>106</v>
+      </c>
+      <c r="D24" s="39" t="s">
+        <v>107</v>
+      </c>
+      <c r="E24" s="40" t="s">
+        <v>108</v>
+      </c>
+      <c r="H24" s="38" t="s">
+        <v>55</v>
+      </c>
+      <c r="I24" s="39" t="s">
+        <v>106</v>
+      </c>
+      <c r="J24" s="39" t="s">
+        <v>107</v>
+      </c>
+      <c r="K24" s="40" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="25" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B25" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="E25" s="29" t="s">
+        <v>110</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="J25" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="K25" s="29" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="26" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B26" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="E26" s="30" t="s">
+        <v>202</v>
+      </c>
+      <c r="H26" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="I26" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="J26" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="K26" s="33" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="27" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B27" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="28" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B28" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E28" s="4"/>
+      <c r="H28" s="35" t="s">
+        <v>194</v>
+      </c>
+      <c r="I28" s="36" t="s">
+        <v>105</v>
+      </c>
+      <c r="J28" s="36"/>
+      <c r="K28" s="37"/>
+    </row>
+    <row r="29" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B29" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E29" s="4"/>
+      <c r="H29" s="38" t="s">
+        <v>55</v>
+      </c>
+      <c r="I29" s="39" t="s">
+        <v>106</v>
+      </c>
+      <c r="J29" s="39" t="s">
+        <v>107</v>
+      </c>
+      <c r="K29" s="40" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="30" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B30" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="E30" s="7"/>
+      <c r="H30" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="I30" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="J30" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="K30" s="29" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="31" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H31" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="I31" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="J31" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="K31" s="32" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="32" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B32" s="35" t="s">
+        <v>43</v>
+      </c>
+      <c r="C32" s="36" t="s">
+        <v>160</v>
+      </c>
+      <c r="D32" s="36" t="s">
+        <v>198</v>
+      </c>
+      <c r="E32" s="37"/>
+      <c r="H32" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="I32" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="J32" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="K32" s="33" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="33" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B33" s="38" t="s">
+        <v>55</v>
+      </c>
+      <c r="C33" s="39" t="s">
+        <v>106</v>
+      </c>
+      <c r="D33" s="39" t="s">
+        <v>107</v>
+      </c>
+      <c r="E33" s="40" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="34" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B34" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="E34" s="30" t="s">
+        <v>202</v>
+      </c>
+      <c r="H34" s="35" t="s">
+        <v>120</v>
+      </c>
+      <c r="I34" s="36" t="s">
+        <v>121</v>
+      </c>
+      <c r="J34" s="36"/>
+      <c r="K34" s="37"/>
+    </row>
+    <row r="35" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B35" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="E35" s="30" t="s">
+        <v>202</v>
+      </c>
+      <c r="H35" s="38" t="s">
+        <v>55</v>
+      </c>
+      <c r="I35" s="39" t="s">
+        <v>106</v>
+      </c>
+      <c r="J35" s="39" t="s">
+        <v>107</v>
+      </c>
+      <c r="K35" s="40" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="36" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B36" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="C36" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="D36" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="E36" s="7"/>
+      <c r="H36" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="I36" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="J36" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="K36" s="29" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="37" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="H37" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="I37" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="J37" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="K37" s="30" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="38" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H38" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="I38" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="J38" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="K38" s="4"/>
+    </row>
+    <row r="39" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B39" s="35" t="s">
+        <v>9</v>
+      </c>
+      <c r="C39" s="36" t="s">
+        <v>170</v>
+      </c>
+      <c r="D39" s="36"/>
+      <c r="E39" s="37"/>
+      <c r="H39" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="I39" s="34" t="s">
+        <v>132</v>
+      </c>
+      <c r="J39" s="34" t="s">
+        <v>203</v>
+      </c>
+      <c r="K39" s="4"/>
+    </row>
+    <row r="40" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B40" s="38" t="s">
+        <v>55</v>
+      </c>
+      <c r="C40" s="39" t="s">
+        <v>106</v>
+      </c>
+      <c r="D40" s="39" t="s">
+        <v>107</v>
+      </c>
+      <c r="E40" s="40" t="s">
+        <v>108</v>
+      </c>
+      <c r="H40" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I40" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="J40" s="34" t="s">
+        <v>203</v>
+      </c>
+      <c r="K40" s="4"/>
+    </row>
+    <row r="41" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B41" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="E41" s="29" t="s">
+        <v>110</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="I41" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="J41" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="K41" s="4" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="42" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B42" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E42" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="H42" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="I42" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="J42" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="K42" s="7" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="43" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B43" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="E43" s="4" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="44" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B44" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="E44" s="4" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="45" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B45" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="D45" s="34" t="s">
+        <v>203</v>
+      </c>
+      <c r="E45" s="4"/>
+      <c r="H45" s="35" t="s">
+        <v>143</v>
+      </c>
+      <c r="I45" s="36" t="s">
+        <v>144</v>
+      </c>
+      <c r="J45" s="36"/>
+      <c r="K45" s="37"/>
+    </row>
+    <row r="46" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B46" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="E46" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="H46" s="38" t="s">
+        <v>55</v>
+      </c>
+      <c r="I46" s="39" t="s">
+        <v>106</v>
+      </c>
+      <c r="J46" s="39" t="s">
+        <v>107</v>
+      </c>
+      <c r="K46" s="40" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="47" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B47" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="C47" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="D47" s="34" t="s">
+        <v>203</v>
+      </c>
+      <c r="E47" s="7"/>
+      <c r="H47" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I47" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="J47" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="K47" s="29" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="48" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H48" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="I48" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="J48" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="K48" s="30" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="49" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B49" s="35" t="s">
+        <v>20</v>
+      </c>
+      <c r="C49" s="36" t="s">
+        <v>180</v>
+      </c>
+      <c r="D49" s="36"/>
+      <c r="E49" s="37"/>
+      <c r="H49" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="I49" s="34" t="s">
+        <v>148</v>
+      </c>
+      <c r="J49" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="K49" s="4"/>
+    </row>
+    <row r="50" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B50" s="38" t="s">
+        <v>55</v>
+      </c>
+      <c r="C50" s="39" t="s">
+        <v>106</v>
+      </c>
+      <c r="D50" s="39" t="s">
+        <v>107</v>
+      </c>
+      <c r="E50" s="40" t="s">
+        <v>108</v>
+      </c>
+      <c r="H50" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="I50" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="J50" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="K50" s="30" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="51" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B51" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="E51" s="30" t="s">
+        <v>202</v>
+      </c>
+      <c r="H51" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="I51" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="J51" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="K51" s="7" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="52" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B52" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="E52" s="30" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="53" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B53" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="C53" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="D53" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="E53" s="7"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1EC1A73-CE70-4415-A446-32DCA71A6530}">
   <dimension ref="A1:G65"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -1967,9 +3456,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87580854-C28E-4E95-AB15-75B01A5EA365}">
-  <dimension ref="B2:J53"/>
+  <dimension ref="B2:L53"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3.25" customWidth="1"/>
@@ -1977,59 +3466,60 @@
     <col min="3" max="3" width="16.75" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="17.125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="19.125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="2.125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.5" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="19.125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="2.125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="7.125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="11.625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="16.75" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="17.125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="18.875" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="16" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="8" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="11.625" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="7.125" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="15.875" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="9.625" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="8.125" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="17.125" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="7.125" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="16.625" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="11" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="8" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="11.625" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="7.125" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="11" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="7.625" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="14.875" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="7.125" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="15.125" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="9.625" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="8" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="11.625" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="7.125" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="17.25" bestFit="1" customWidth="1"/>
-    <col min="54" max="54" width="13.75" bestFit="1" customWidth="1"/>
-    <col min="55" max="55" width="13.125" bestFit="1" customWidth="1"/>
-    <col min="56" max="56" width="16" bestFit="1" customWidth="1"/>
-    <col min="57" max="57" width="7.125" bestFit="1" customWidth="1"/>
-    <col min="59" max="59" width="18" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="8.75" bestFit="1" customWidth="1"/>
-    <col min="61" max="61" width="5" bestFit="1" customWidth="1"/>
-    <col min="62" max="62" width="11.625" bestFit="1" customWidth="1"/>
-    <col min="63" max="63" width="7.125" bestFit="1" customWidth="1"/>
-    <col min="68" max="68" width="13" bestFit="1" customWidth="1"/>
-    <col min="70" max="70" width="7.5" bestFit="1" customWidth="1"/>
-    <col min="71" max="71" width="7.125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.25" customWidth="1"/>
+    <col min="7" max="7" width="2.125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="19.125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="2.125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7.125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="15.875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="11.625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="16.75" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="17.125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="18.875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="16" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="8" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="11.625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="7.125" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="15.875" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="9.625" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="8.125" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="17.125" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="7.125" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="16.625" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="11" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="8" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="11.625" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="7.125" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="11" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="7.625" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="14.875" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="7.125" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="15.125" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="9.625" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="8" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="11.625" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="7.125" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="17.25" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="13.75" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="13.125" bestFit="1" customWidth="1"/>
+    <col min="57" max="57" width="16" bestFit="1" customWidth="1"/>
+    <col min="58" max="58" width="7.125" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="18" bestFit="1" customWidth="1"/>
+    <col min="61" max="61" width="8.75" bestFit="1" customWidth="1"/>
+    <col min="62" max="62" width="5" bestFit="1" customWidth="1"/>
+    <col min="63" max="63" width="11.625" bestFit="1" customWidth="1"/>
+    <col min="64" max="64" width="7.125" bestFit="1" customWidth="1"/>
+    <col min="69" max="69" width="13" bestFit="1" customWidth="1"/>
+    <col min="71" max="71" width="7.5" bestFit="1" customWidth="1"/>
+    <col min="72" max="72" width="7.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="3" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B3" s="10" t="s">
         <v>8</v>
       </c>
@@ -2038,16 +3528,17 @@
       </c>
       <c r="D3" s="11"/>
       <c r="E3" s="12"/>
-      <c r="G3" s="10" t="s">
+      <c r="F3" s="21"/>
+      <c r="H3" s="10" t="s">
         <v>104</v>
       </c>
-      <c r="H3" s="11" t="s">
+      <c r="I3" s="11" t="s">
         <v>105</v>
       </c>
-      <c r="I3" s="11"/>
-      <c r="J3" s="12"/>
-    </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="J3" s="11"/>
+      <c r="K3" s="12"/>
+    </row>
+    <row r="4" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B4" s="13" t="s">
         <v>55</v>
       </c>
@@ -2060,20 +3551,21 @@
       <c r="E4" s="15" t="s">
         <v>108</v>
       </c>
-      <c r="G4" s="13" t="s">
+      <c r="F4" s="21"/>
+      <c r="H4" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="H4" s="14" t="s">
+      <c r="I4" s="14" t="s">
         <v>106</v>
       </c>
-      <c r="I4" s="14" t="s">
+      <c r="J4" s="14" t="s">
         <v>107</v>
       </c>
-      <c r="J4" s="15" t="s">
+      <c r="K4" s="15" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B5" s="3" t="s">
         <v>182</v>
       </c>
@@ -2086,20 +3578,22 @@
       <c r="E5" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="F5" s="23"/>
+      <c r="H5" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="H5" s="1" t="s">
+      <c r="I5" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="I5" s="1" t="s">
+      <c r="J5" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="J5" s="4" t="s">
+      <c r="K5" s="4" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="6" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L5" s="23"/>
+    </row>
+    <row r="6" spans="2:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B6" s="3" t="s">
         <v>68</v>
       </c>
@@ -2112,18 +3606,19 @@
       <c r="E6" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="G6" s="5" t="s">
+      <c r="F6" s="23"/>
+      <c r="H6" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="H6" s="6" t="s">
+      <c r="I6" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="I6" s="6" t="s">
+      <c r="J6" s="6" t="s">
         <v>117</v>
       </c>
-      <c r="J6" s="7"/>
-    </row>
-    <row r="7" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="K6" s="7"/>
+    </row>
+    <row r="7" spans="2:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B7" s="3" t="s">
         <v>62</v>
       </c>
@@ -2136,9 +3631,10 @@
       <c r="E7" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="F7" s="8"/>
-    </row>
-    <row r="8" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="F7" s="23"/>
+      <c r="G7" s="8"/>
+    </row>
+    <row r="8" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B8" s="3" t="s">
         <v>32</v>
       </c>
@@ -2151,16 +3647,17 @@
       <c r="E8" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="G8" s="10" t="s">
+      <c r="F8" s="23"/>
+      <c r="H8" s="10" t="s">
         <v>120</v>
       </c>
-      <c r="H8" s="11" t="s">
+      <c r="I8" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="I8" s="11"/>
-      <c r="J8" s="12"/>
-    </row>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="J8" s="11"/>
+      <c r="K8" s="12"/>
+    </row>
+    <row r="9" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B9" s="3" t="s">
         <v>33</v>
       </c>
@@ -2173,20 +3670,21 @@
       <c r="E9" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="G9" s="13" t="s">
+      <c r="F9" s="23"/>
+      <c r="H9" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="H9" s="14" t="s">
+      <c r="I9" s="14" t="s">
         <v>106</v>
       </c>
-      <c r="I9" s="14" t="s">
+      <c r="J9" s="14" t="s">
         <v>107</v>
       </c>
-      <c r="J9" s="15" t="s">
+      <c r="K9" s="15" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B10" s="3" t="s">
         <v>34</v>
       </c>
@@ -2199,20 +3697,22 @@
       <c r="E10" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="G10" s="3" t="s">
+      <c r="F10" s="23"/>
+      <c r="H10" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="H10" s="1" t="s">
+      <c r="I10" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="I10" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J10" s="4" t="s">
+      <c r="J10" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="K10" s="4" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="L10" s="23"/>
+    </row>
+    <row r="11" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B11" s="3" t="s">
         <v>126</v>
       </c>
@@ -2225,20 +3725,22 @@
       <c r="E11" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="G11" s="3" t="s">
+      <c r="F11" s="23"/>
+      <c r="H11" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="H11" s="1" t="s">
+      <c r="I11" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="I11" s="1" t="s">
+      <c r="J11" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="J11" s="4" t="s">
+      <c r="K11" s="4" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="12" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="L11" s="23"/>
+    </row>
+    <row r="12" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B12" s="3" t="s">
         <v>186</v>
       </c>
@@ -2251,179 +3753,203 @@
       <c r="E12" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="G12" s="3" t="s">
+      <c r="F12" s="23"/>
+      <c r="H12" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="H12" s="1" t="s">
+      <c r="I12" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="I12" s="1" t="s">
+      <c r="J12" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="J12" s="4"/>
-    </row>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B13" s="3" t="s">
+      <c r="K12" s="4"/>
+      <c r="L12" s="23"/>
+    </row>
+    <row r="13" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B13" s="18" t="s">
+        <v>187</v>
+      </c>
+      <c r="C13" s="19" t="s">
+        <v>188</v>
+      </c>
+      <c r="D13" s="19" t="s">
+        <v>83</v>
+      </c>
+      <c r="E13" s="20" t="s">
+        <v>119</v>
+      </c>
+      <c r="F13" s="23"/>
+      <c r="H13" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="K13" s="4"/>
+      <c r="L13" s="23"/>
+    </row>
+    <row r="14" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B14" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="C14" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="D14" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="E13" s="4" t="s">
+      <c r="E14" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="G13" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="H13" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="I13" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="J13" s="4"/>
-    </row>
-    <row r="14" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="5" t="s">
+      <c r="F14" s="23"/>
+      <c r="H14" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="K14" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="L14" s="23"/>
+    </row>
+    <row r="15" spans="2:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B15" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="C14" s="6" t="s">
+      <c r="C15" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="D14" s="6" t="s">
+      <c r="D15" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="E14" s="7"/>
-      <c r="G14" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="H14" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="I14" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="J14" s="4" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="15" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="G15" s="5" t="s">
+      <c r="E15" s="7"/>
+      <c r="F15" s="22"/>
+      <c r="H15" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="H15" s="6" t="s">
+      <c r="I15" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="I15" s="6" t="s">
+      <c r="J15" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="J15" s="7"/>
-    </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B16" s="10" t="s">
+      <c r="K15" s="7"/>
+    </row>
+    <row r="16" spans="2:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="17" spans="2:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B17" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="C16" s="11" t="s">
+      <c r="C17" s="11" t="s">
         <v>141</v>
       </c>
-      <c r="D16" s="11"/>
-      <c r="E16" s="12"/>
-    </row>
-    <row r="17" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B17" s="13" t="s">
+      <c r="D17" s="11"/>
+      <c r="E17" s="12"/>
+      <c r="F17" s="21"/>
+    </row>
+    <row r="18" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B18" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="C17" s="14" t="s">
+      <c r="C18" s="14" t="s">
         <v>106</v>
       </c>
-      <c r="D17" s="14" t="s">
+      <c r="D18" s="14" t="s">
         <v>107</v>
       </c>
-      <c r="E17" s="15" t="s">
+      <c r="E18" s="15" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B18" s="3" t="s">
+      <c r="F18" s="21"/>
+      <c r="H18" s="10" t="s">
+        <v>143</v>
+      </c>
+      <c r="I18" s="11" t="s">
+        <v>144</v>
+      </c>
+      <c r="J18" s="11"/>
+      <c r="K18" s="12"/>
+    </row>
+    <row r="19" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B19" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="C19" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="D18" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="E18" s="4" t="s">
+      <c r="D19" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="E19" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="G18" s="10" t="s">
-        <v>143</v>
-      </c>
-      <c r="H18" s="11" t="s">
-        <v>144</v>
-      </c>
-      <c r="I18" s="11"/>
-      <c r="J18" s="12"/>
-    </row>
-    <row r="19" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B19" s="5" t="s">
+      <c r="F19" s="23"/>
+      <c r="H19" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="I19" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="J19" s="14" t="s">
+        <v>107</v>
+      </c>
+      <c r="K19" s="15" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="20" spans="2:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B20" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="C19" s="6" t="s">
+      <c r="C20" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="D19" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="E19" s="7" t="s">
+      <c r="D20" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="E20" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="G19" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="H19" s="14" t="s">
-        <v>106</v>
-      </c>
-      <c r="I19" s="14" t="s">
-        <v>107</v>
-      </c>
-      <c r="J19" s="15" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.3">
       <c r="F20" s="9"/>
-      <c r="G20" s="3" t="s">
+      <c r="G20" s="9"/>
+      <c r="H20" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="H20" s="1" t="s">
+      <c r="I20" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="I20" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J20" s="4" t="s">
+      <c r="J20" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="K20" s="4" t="s">
         <v>146</v>
       </c>
-    </row>
-    <row r="21" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="G21" s="3" t="s">
+      <c r="L20" s="23"/>
+    </row>
+    <row r="21" spans="2:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H21" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="H21" s="1" t="s">
+      <c r="I21" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="I21" s="1" t="s">
+      <c r="J21" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="J21" s="4" t="s">
+      <c r="K21" s="4" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="L21" s="23"/>
+    </row>
+    <row r="22" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B22" s="10" t="s">
         <v>6</v>
       </c>
@@ -2432,18 +3958,20 @@
       </c>
       <c r="D22" s="11"/>
       <c r="E22" s="12"/>
-      <c r="G22" s="3" t="s">
+      <c r="F22" s="21"/>
+      <c r="H22" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="H22" s="1" t="s">
+      <c r="I22" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="I22" s="1" t="s">
+      <c r="J22" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="J22" s="4"/>
-    </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K22" s="4"/>
+      <c r="L22" s="23"/>
+    </row>
+    <row r="23" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B23" s="13" t="s">
         <v>55</v>
       </c>
@@ -2456,20 +3984,22 @@
       <c r="E23" s="15" t="s">
         <v>108</v>
       </c>
-      <c r="G23" s="3" t="s">
+      <c r="F23" s="21"/>
+      <c r="H23" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="H23" s="1" t="s">
+      <c r="I23" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="I23" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J23" s="4" t="s">
+      <c r="J23" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="K23" s="4" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="24" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L23" s="23"/>
+    </row>
+    <row r="24" spans="2:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B24" s="3" t="s">
         <v>37</v>
       </c>
@@ -2482,20 +4012,21 @@
       <c r="E24" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="G24" s="5" t="s">
+      <c r="F24" s="23"/>
+      <c r="H24" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="H24" s="6" t="s">
+      <c r="I24" s="6" t="s">
         <v>150</v>
       </c>
-      <c r="I24" s="6" t="s">
+      <c r="J24" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="J24" s="7" t="s">
+      <c r="K24" s="7" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="25" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B25" s="3" t="s">
         <v>70</v>
       </c>
@@ -2508,8 +4039,9 @@
       <c r="E25" s="4" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="26" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="F25" s="23"/>
+    </row>
+    <row r="26" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B26" s="3" t="s">
         <v>41</v>
       </c>
@@ -2522,16 +4054,17 @@
       <c r="E26" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="G26" s="10" t="s">
+      <c r="F26" s="23"/>
+      <c r="H26" s="10" t="s">
         <v>152</v>
       </c>
-      <c r="H26" s="11" t="s">
+      <c r="I26" s="11" t="s">
         <v>153</v>
       </c>
-      <c r="I26" s="16"/>
-      <c r="J26" s="17"/>
-    </row>
-    <row r="27" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="J26" s="16"/>
+      <c r="K26" s="17"/>
+    </row>
+    <row r="27" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B27" s="3" t="s">
         <v>126</v>
       </c>
@@ -2544,20 +4077,21 @@
       <c r="E27" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="G27" s="13" t="s">
+      <c r="F27" s="23"/>
+      <c r="H27" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="H27" s="14" t="s">
+      <c r="I27" s="14" t="s">
         <v>106</v>
       </c>
-      <c r="I27" s="14" t="s">
+      <c r="J27" s="14" t="s">
         <v>107</v>
       </c>
-      <c r="J27" s="15" t="s">
+      <c r="K27" s="15" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="28" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B28" s="3" t="s">
         <v>186</v>
       </c>
@@ -2570,20 +4104,22 @@
       <c r="E28" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="G28" s="3" t="s">
+      <c r="F28" s="23"/>
+      <c r="H28" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="H28" s="1" t="s">
+      <c r="I28" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="I28" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J28" s="4" t="s">
+      <c r="J28" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="K28" s="4" t="s">
         <v>146</v>
       </c>
-    </row>
-    <row r="29" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="L28" s="23"/>
+    </row>
+    <row r="29" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B29" s="3" t="s">
         <v>92</v>
       </c>
@@ -2596,18 +4132,20 @@
       <c r="E29" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="G29" s="3" t="s">
+      <c r="F29" s="23"/>
+      <c r="H29" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="H29" s="1" t="s">
+      <c r="I29" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="I29" s="1" t="s">
+      <c r="J29" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="J29" s="4"/>
-    </row>
-    <row r="30" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="K29" s="4"/>
+      <c r="L29" s="23"/>
+    </row>
+    <row r="30" spans="2:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B30" s="5" t="s">
         <v>94</v>
       </c>
@@ -2618,31 +4156,34 @@
         <v>96</v>
       </c>
       <c r="E30" s="7"/>
-      <c r="G30" s="3" t="s">
+      <c r="F30" s="22"/>
+      <c r="H30" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="H30" s="1" t="s">
+      <c r="I30" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="I30" s="1" t="s">
+      <c r="J30" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="J30" s="4"/>
-    </row>
-    <row r="31" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="F31" s="9"/>
-      <c r="G31" s="3" t="s">
+      <c r="K30" s="4"/>
+      <c r="L30" s="23"/>
+    </row>
+    <row r="31" spans="2:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="G31" s="9"/>
+      <c r="H31" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="H31" s="1" t="s">
+      <c r="I31" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="I31" s="1" t="s">
+      <c r="J31" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="J31" s="4"/>
-    </row>
-    <row r="32" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K31" s="4"/>
+      <c r="L31" s="23"/>
+    </row>
+    <row r="32" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B32" s="10" t="s">
         <v>43</v>
       </c>
@@ -2651,18 +4192,20 @@
       </c>
       <c r="D32" s="11"/>
       <c r="E32" s="12"/>
-      <c r="G32" s="3" t="s">
+      <c r="F32" s="21"/>
+      <c r="H32" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="H32" s="1" t="s">
+      <c r="I32" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="I32" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J32" s="4"/>
-    </row>
-    <row r="33" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="J32" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="K32" s="4"/>
+      <c r="L32" s="23"/>
+    </row>
+    <row r="33" spans="2:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B33" s="13" t="s">
         <v>55</v>
       </c>
@@ -2675,20 +4218,21 @@
       <c r="E33" s="15" t="s">
         <v>108</v>
       </c>
-      <c r="G33" s="5" t="s">
+      <c r="F33" s="21"/>
+      <c r="H33" s="5" t="s">
         <v>162</v>
       </c>
-      <c r="H33" s="6" t="s">
+      <c r="I33" s="6" t="s">
         <v>185</v>
       </c>
-      <c r="I33" s="6" t="s">
+      <c r="J33" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="J33" s="7" t="s">
+      <c r="K33" s="7" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="34" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B34" s="3" t="s">
         <v>37</v>
       </c>
@@ -2701,8 +4245,9 @@
       <c r="E34" s="4" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="35" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="F34" s="23"/>
+    </row>
+    <row r="35" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B35" s="3" t="s">
         <v>44</v>
       </c>
@@ -2715,16 +4260,17 @@
       <c r="E35" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="G35" s="10" t="s">
+      <c r="F35" s="23"/>
+      <c r="H35" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="H35" s="11" t="s">
+      <c r="I35" s="11" t="s">
         <v>166</v>
       </c>
-      <c r="I35" s="11"/>
-      <c r="J35" s="12"/>
-    </row>
-    <row r="36" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="J35" s="11"/>
+      <c r="K35" s="12"/>
+    </row>
+    <row r="36" spans="2:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B36" s="5" t="s">
         <v>167</v>
       </c>
@@ -2735,48 +4281,51 @@
         <v>100</v>
       </c>
       <c r="E36" s="7"/>
-      <c r="G36" s="13" t="s">
+      <c r="F36" s="22"/>
+      <c r="H36" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="H36" s="14" t="s">
+      <c r="I36" s="14" t="s">
         <v>106</v>
       </c>
-      <c r="I36" s="14" t="s">
+      <c r="J36" s="14" t="s">
         <v>107</v>
       </c>
-      <c r="J36" s="15" t="s">
+      <c r="K36" s="15" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="37" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="G37" s="3" t="s">
+    <row r="37" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="H37" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="H37" s="1" t="s">
+      <c r="I37" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="I37" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J37" s="4" t="s">
+      <c r="J37" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="K37" s="4" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="38" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="G38" s="5" t="s">
+      <c r="L37" s="23"/>
+    </row>
+    <row r="38" spans="2:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H38" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="H38" s="6" t="s">
+      <c r="I38" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="I38" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="J38" s="7" t="s">
+      <c r="J38" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="K38" s="7" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="39" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L38" s="23"/>
+    </row>
+    <row r="39" spans="2:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B39" s="10" t="s">
         <v>9</v>
       </c>
@@ -2785,8 +4334,9 @@
       </c>
       <c r="D39" s="11"/>
       <c r="E39" s="12"/>
-    </row>
-    <row r="40" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="F39" s="21"/>
+    </row>
+    <row r="40" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B40" s="13" t="s">
         <v>55</v>
       </c>
@@ -2799,16 +4349,17 @@
       <c r="E40" s="15" t="s">
         <v>108</v>
       </c>
-      <c r="G40" s="10" t="s">
+      <c r="F40" s="21"/>
+      <c r="H40" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="H40" s="11" t="s">
+      <c r="I40" s="11" t="s">
         <v>171</v>
       </c>
-      <c r="I40" s="11"/>
-      <c r="J40" s="12"/>
-    </row>
-    <row r="41" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="J40" s="11"/>
+      <c r="K40" s="12"/>
+    </row>
+    <row r="41" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B41" s="3" t="s">
         <v>42</v>
       </c>
@@ -2821,20 +4372,21 @@
       <c r="E41" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="G41" s="13" t="s">
+      <c r="F41" s="23"/>
+      <c r="H41" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="H41" s="14" t="s">
+      <c r="I41" s="14" t="s">
         <v>106</v>
       </c>
-      <c r="I41" s="14" t="s">
+      <c r="J41" s="14" t="s">
         <v>107</v>
       </c>
-      <c r="J41" s="15" t="s">
+      <c r="K41" s="15" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="42" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B42" s="3" t="s">
         <v>46</v>
       </c>
@@ -2847,20 +4399,22 @@
       <c r="E42" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="G42" s="3" t="s">
+      <c r="F42" s="23"/>
+      <c r="H42" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="H42" s="1" t="s">
+      <c r="I42" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="I42" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J42" s="4" t="s">
+      <c r="J42" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="K42" s="4" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="43" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L42" s="23"/>
+    </row>
+    <row r="43" spans="2:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B43" s="3" t="s">
         <v>47</v>
       </c>
@@ -2873,20 +4427,21 @@
       <c r="E43" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="G43" s="5" t="s">
+      <c r="F43" s="23"/>
+      <c r="H43" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="H43" s="6" t="s">
+      <c r="I43" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="I43" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="J43" s="7" t="s">
+      <c r="J43" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="K43" s="7" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="44" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B44" s="3" t="s">
         <v>48</v>
       </c>
@@ -2899,8 +4454,9 @@
       <c r="E44" s="4" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="45" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="F44" s="23"/>
+    </row>
+    <row r="45" spans="2:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B45" s="3" t="s">
         <v>97</v>
       </c>
@@ -2911,8 +4467,9 @@
         <v>133</v>
       </c>
       <c r="E45" s="4"/>
-    </row>
-    <row r="46" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="F45" s="23"/>
+    </row>
+    <row r="46" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B46" s="3" t="s">
         <v>162</v>
       </c>
@@ -2925,16 +4482,17 @@
       <c r="E46" s="4" t="s">
         <v>164</v>
       </c>
-      <c r="G46" s="10" t="s">
+      <c r="F46" s="23"/>
+      <c r="H46" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="H46" s="11" t="s">
+      <c r="I46" s="11" t="s">
         <v>177</v>
       </c>
-      <c r="I46" s="11"/>
-      <c r="J46" s="12"/>
-    </row>
-    <row r="47" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="J46" s="11"/>
+      <c r="K46" s="12"/>
+    </row>
+    <row r="47" spans="2:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B47" s="5" t="s">
         <v>178</v>
       </c>
@@ -2945,34 +4503,35 @@
         <v>133</v>
       </c>
       <c r="E47" s="7"/>
-      <c r="G47" s="13" t="s">
+      <c r="F47" s="22"/>
+      <c r="H47" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="H47" s="14" t="s">
+      <c r="I47" s="14" t="s">
         <v>106</v>
       </c>
-      <c r="I47" s="14" t="s">
+      <c r="J47" s="14" t="s">
         <v>107</v>
       </c>
-      <c r="J47" s="15" t="s">
+      <c r="K47" s="15" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="48" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="G48" s="3" t="s">
+    <row r="48" spans="2:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H48" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="H48" s="1" t="s">
+      <c r="I48" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="I48" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J48" s="4" t="s">
+      <c r="J48" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="K48" s="4" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="49" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B49" s="10" t="s">
         <v>20</v>
       </c>
@@ -2981,20 +4540,21 @@
       </c>
       <c r="D49" s="11"/>
       <c r="E49" s="12"/>
-      <c r="G49" s="5" t="s">
+      <c r="F49" s="21"/>
+      <c r="H49" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="H49" s="6" t="s">
+      <c r="I49" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="I49" s="6" t="s">
+      <c r="J49" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="J49" s="7" t="s">
+      <c r="K49" s="7" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="50" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B50" s="13" t="s">
         <v>55</v>
       </c>
@@ -3007,8 +4567,9 @@
       <c r="E50" s="15" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="51" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="F50" s="21"/>
+    </row>
+    <row r="51" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B51" s="3" t="s">
         <v>182</v>
       </c>
@@ -3021,8 +4582,9 @@
       <c r="E51" s="4" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="52" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="F51" s="23"/>
+    </row>
+    <row r="52" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B52" s="3" t="s">
         <v>52</v>
       </c>
@@ -3035,8 +4597,9 @@
       <c r="E52" s="4" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="53" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="F52" s="23"/>
+    </row>
+    <row r="53" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B53" s="5" t="s">
         <v>53</v>
       </c>
@@ -3047,9 +4610,1180 @@
         <v>100</v>
       </c>
       <c r="E53" s="7"/>
+      <c r="F53" s="22"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1938069A-9289-43BA-84C8-6BC33CEB5604}">
+  <dimension ref="B2:R53"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="3.25" customWidth="1"/>
+    <col min="2" max="2" width="22.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.75" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.25" customWidth="1"/>
+    <col min="7" max="7" width="2.125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="19.125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="2.125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7.125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="24.375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="17.125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="39.5" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="2.125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="17.125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="18.875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="16" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="8" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="11.625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="7.125" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="15.875" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="9.625" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="8.125" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="17.125" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="7.125" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="16.625" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="11" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="8" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="11.625" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="7.125" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="11" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="7.625" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="14.875" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="7.125" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="15.125" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="9.625" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="8" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="11.625" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="7.125" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="17.25" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="13.75" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="13.125" bestFit="1" customWidth="1"/>
+    <col min="57" max="57" width="16" bestFit="1" customWidth="1"/>
+    <col min="58" max="58" width="7.125" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="18" bestFit="1" customWidth="1"/>
+    <col min="61" max="61" width="8.75" bestFit="1" customWidth="1"/>
+    <col min="62" max="62" width="5" bestFit="1" customWidth="1"/>
+    <col min="63" max="63" width="11.625" bestFit="1" customWidth="1"/>
+    <col min="64" max="64" width="7.125" bestFit="1" customWidth="1"/>
+    <col min="69" max="69" width="13" bestFit="1" customWidth="1"/>
+    <col min="71" max="71" width="7.5" bestFit="1" customWidth="1"/>
+    <col min="72" max="72" width="7.125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:18" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="3" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B3" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="D3" s="11"/>
+      <c r="E3" s="12"/>
+      <c r="H3" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="I3" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="J3" s="16"/>
+      <c r="K3" s="17"/>
+    </row>
+    <row r="4" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B4" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="D4" s="14" t="s">
+        <v>107</v>
+      </c>
+      <c r="E4" s="15" t="s">
+        <v>108</v>
+      </c>
+      <c r="H4" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="I4" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="J4" s="14" t="s">
+        <v>107</v>
+      </c>
+      <c r="K4" s="15" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="5" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B5" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="E5" s="29" t="s">
+        <v>110</v>
+      </c>
+      <c r="F5" s="23"/>
+      <c r="H5" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="K5" s="29" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="6" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B6" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="E6" s="32" t="s">
+        <v>197</v>
+      </c>
+      <c r="F6" s="23"/>
+      <c r="H6" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="K6" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="R6" s="23" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="7" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B7" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="F7" s="23"/>
+      <c r="H7" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="K7" s="4"/>
+      <c r="R7" s="23" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="8" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B8" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="F8" s="23"/>
+      <c r="H8" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="K8" s="4"/>
+      <c r="R8" s="23" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="9" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B9" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="F9" s="23"/>
+      <c r="H9" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="K9" s="4"/>
+      <c r="R9" s="23" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="10" spans="2:18" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B10" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E10" s="32" t="s">
+        <v>197</v>
+      </c>
+      <c r="F10" s="23"/>
+      <c r="H10" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="I10" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="J10" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="K10" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="R10" s="23" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="11" spans="2:18" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B11" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="F11" s="23"/>
+      <c r="R11" s="23" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="12" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B12" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="F12" s="23"/>
+      <c r="H12" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="I12" s="11" t="s">
+        <v>166</v>
+      </c>
+      <c r="J12" s="11"/>
+      <c r="K12" s="12"/>
+      <c r="R12" s="23" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="13" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B13" s="25" t="s">
+        <v>187</v>
+      </c>
+      <c r="C13" s="24" t="s">
+        <v>188</v>
+      </c>
+      <c r="D13" s="24" t="s">
+        <v>83</v>
+      </c>
+      <c r="E13" s="26" t="s">
+        <v>119</v>
+      </c>
+      <c r="F13" s="23"/>
+      <c r="H13" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="I13" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="J13" s="14" t="s">
+        <v>107</v>
+      </c>
+      <c r="K13" s="15" t="s">
+        <v>108</v>
+      </c>
+      <c r="R13" s="23" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="14" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B14" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="F14" s="23"/>
+      <c r="H14" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="K14" s="30" t="s">
+        <v>202</v>
+      </c>
+      <c r="R14" s="23" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="15" spans="2:18" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B15" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="F15" s="23"/>
+      <c r="H15" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="I15" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="J15" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="K15" s="31" t="s">
+        <v>202</v>
+      </c>
+      <c r="R15" s="23" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="16" spans="2:18" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B16" s="27" t="s">
+        <v>108</v>
+      </c>
+      <c r="C16" s="28" t="s">
+        <v>200</v>
+      </c>
+      <c r="D16" s="28" t="s">
+        <v>96</v>
+      </c>
+      <c r="E16" s="7"/>
+      <c r="F16" s="23"/>
+      <c r="R16" s="23" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="17" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H17" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="I17" s="11" t="s">
+        <v>171</v>
+      </c>
+      <c r="J17" s="11"/>
+      <c r="K17" s="12"/>
+    </row>
+    <row r="18" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B18" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C18" s="11" t="s">
+        <v>141</v>
+      </c>
+      <c r="D18" s="11" t="s">
+        <v>198</v>
+      </c>
+      <c r="E18" s="12"/>
+      <c r="H18" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="I18" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="J18" s="14" t="s">
+        <v>107</v>
+      </c>
+      <c r="K18" s="15" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="19" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B19" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="C19" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="D19" s="14" t="s">
+        <v>107</v>
+      </c>
+      <c r="E19" s="15" t="s">
+        <v>108</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="J19" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="K19" s="30" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="20" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B20" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="E20" s="30" t="s">
+        <v>202</v>
+      </c>
+      <c r="H20" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="I20" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="J20" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="K20" s="31" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="21" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B21" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="E21" s="31" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="22" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="23" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B23" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="C23" s="11" t="s">
+        <v>147</v>
+      </c>
+      <c r="D23" s="11"/>
+      <c r="E23" s="12"/>
+      <c r="H23" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="I23" s="11" t="s">
+        <v>177</v>
+      </c>
+      <c r="J23" s="11"/>
+      <c r="K23" s="12"/>
+    </row>
+    <row r="24" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B24" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="C24" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="D24" s="14" t="s">
+        <v>107</v>
+      </c>
+      <c r="E24" s="15" t="s">
+        <v>108</v>
+      </c>
+      <c r="H24" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="I24" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="J24" s="14" t="s">
+        <v>107</v>
+      </c>
+      <c r="K24" s="15" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="25" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B25" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="E25" s="29" t="s">
+        <v>110</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="J25" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="K25" s="29" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="26" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B26" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="E26" s="30" t="s">
+        <v>202</v>
+      </c>
+      <c r="H26" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="I26" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="J26" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="K26" s="33" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="27" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B27" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="28" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B28" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E28" s="4"/>
+      <c r="H28" s="10" t="s">
+        <v>194</v>
+      </c>
+      <c r="I28" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="J28" s="11"/>
+      <c r="K28" s="12"/>
+    </row>
+    <row r="29" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B29" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E29" s="4"/>
+      <c r="H29" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="I29" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="J29" s="14" t="s">
+        <v>107</v>
+      </c>
+      <c r="K29" s="15" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="30" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B30" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="E30" s="7"/>
+      <c r="H30" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="I30" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="J30" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="K30" s="29" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="31" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H31" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="I31" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="J31" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="K31" s="4"/>
+    </row>
+    <row r="32" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B32" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="C32" s="11" t="s">
+        <v>160</v>
+      </c>
+      <c r="D32" s="11" t="s">
+        <v>198</v>
+      </c>
+      <c r="E32" s="12"/>
+      <c r="H32" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="I32" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="J32" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="K32" s="33" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="33" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B33" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="C33" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="D33" s="14" t="s">
+        <v>107</v>
+      </c>
+      <c r="E33" s="15" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="34" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B34" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="E34" s="30" t="s">
+        <v>202</v>
+      </c>
+      <c r="H34" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="I34" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="J34" s="11"/>
+      <c r="K34" s="12"/>
+    </row>
+    <row r="35" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B35" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="E35" s="30" t="s">
+        <v>202</v>
+      </c>
+      <c r="H35" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="I35" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="J35" s="14" t="s">
+        <v>107</v>
+      </c>
+      <c r="K35" s="15" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="36" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B36" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="C36" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="D36" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="E36" s="7"/>
+      <c r="H36" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="I36" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="J36" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="K36" s="29" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="37" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="H37" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="I37" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="J37" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="K37" s="30" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="38" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H38" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="I38" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="J38" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="K38" s="4"/>
+    </row>
+    <row r="39" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B39" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C39" s="11" t="s">
+        <v>170</v>
+      </c>
+      <c r="D39" s="11"/>
+      <c r="E39" s="12"/>
+      <c r="H39" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="I39" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="J39" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="K39" s="4"/>
+    </row>
+    <row r="40" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B40" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="C40" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="D40" s="14" t="s">
+        <v>107</v>
+      </c>
+      <c r="E40" s="15" t="s">
+        <v>108</v>
+      </c>
+      <c r="H40" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I40" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="J40" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="K40" s="4"/>
+    </row>
+    <row r="41" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B41" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="E41" s="29" t="s">
+        <v>110</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="I41" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="J41" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="K41" s="4" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="42" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B42" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E42" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="H42" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="I42" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="J42" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="K42" s="7" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="43" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B43" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="E43" s="4" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="44" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B44" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="E44" s="4" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="45" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B45" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="E45" s="4"/>
+      <c r="H45" s="10" t="s">
+        <v>143</v>
+      </c>
+      <c r="I45" s="11" t="s">
+        <v>144</v>
+      </c>
+      <c r="J45" s="11"/>
+      <c r="K45" s="12"/>
+    </row>
+    <row r="46" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B46" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="E46" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="H46" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="I46" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="J46" s="14" t="s">
+        <v>107</v>
+      </c>
+      <c r="K46" s="15" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="47" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B47" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="C47" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="D47" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="E47" s="7"/>
+      <c r="H47" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I47" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="J47" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="K47" s="29" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="48" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H48" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="I48" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="J48" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="K48" s="30" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="49" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B49" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C49" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="D49" s="11"/>
+      <c r="E49" s="12"/>
+      <c r="H49" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="I49" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="J49" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="K49" s="4"/>
+    </row>
+    <row r="50" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B50" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="C50" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="D50" s="14" t="s">
+        <v>107</v>
+      </c>
+      <c r="E50" s="15" t="s">
+        <v>108</v>
+      </c>
+      <c r="H50" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="I50" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="J50" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="K50" s="30" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="51" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B51" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="E51" s="30" t="s">
+        <v>202</v>
+      </c>
+      <c r="H51" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="I51" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="J51" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="K51" s="7" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="52" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B52" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="E52" s="30" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="53" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B53" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="C53" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="D53" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="E53" s="7"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/3_작업영역/0_테이블/테이블.xlsx
+++ b/3_작업영역/0_테이블/테이블.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Awsintel4 Repository\AwsIntel4_OWR\K_dessert\3_작업영역\0_테이블\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DA36AED-25A1-47A1-B9B5-61EDBA9ED0D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5840AAD-0FC8-4268-8EBF-85004AB6C976}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{89506D57-ACF2-4766-BACF-4F8058B8758D}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1105" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1061" uniqueCount="211">
   <si>
     <t>index</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -797,10 +797,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>);</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>NUMBER(1,0)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -840,14 +836,40 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>CREATE TABLE MEMBER(</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>FOREIGN KEY</t>
   </si>
   <si>
     <t>CLOB</t>
+  </si>
+  <si>
+    <t>F_VIEW</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>상품번호</t>
+  </si>
+  <si>
+    <t>태그번호</t>
+  </si>
+  <si>
+    <t>회원번호</t>
+  </si>
+  <si>
+    <t>처리번호</t>
+  </si>
+  <si>
+    <t>다과번호</t>
+  </si>
+  <si>
+    <t>게시판번호</t>
+  </si>
+  <si>
+    <t>답변번호</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>VARCHAR2(50)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -909,7 +931,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="18">
+  <borders count="19">
     <border>
       <left/>
       <right/>
@@ -1136,13 +1158,22 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1270,6 +1301,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="14" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1586,7 +1623,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09F92FCC-166C-4E7D-84B0-227CCB7DD483}">
-  <dimension ref="B2:R53"/>
+  <dimension ref="B2:K53"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3.25" customWidth="1"/>
@@ -1647,8 +1684,8 @@
     <col min="72" max="72" width="7.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:18" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="3" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="3" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B3" s="35" t="s">
         <v>8</v>
       </c>
@@ -1666,7 +1703,7 @@
       <c r="J3" s="41"/>
       <c r="K3" s="42"/>
     </row>
-    <row r="4" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B4" s="38" t="s">
         <v>55</v>
       </c>
@@ -1692,9 +1729,9 @@
         <v>108</v>
       </c>
     </row>
-    <row r="5" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B5" s="3" t="s">
-        <v>182</v>
+        <v>205</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>109</v>
@@ -1707,7 +1744,7 @@
       </c>
       <c r="F5" s="23"/>
       <c r="H5" s="3" t="s">
-        <v>154</v>
+        <v>207</v>
       </c>
       <c r="I5" s="1" t="s">
         <v>155</v>
@@ -1718,11 +1755,8 @@
       <c r="K5" s="29" t="s">
         <v>110</v>
       </c>
-      <c r="O5" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="6" spans="2:18" x14ac:dyDescent="0.3">
+    </row>
+    <row r="6" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B6" s="3" t="s">
         <v>68</v>
       </c>
@@ -1730,10 +1764,10 @@
         <v>113</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>81</v>
+        <v>210</v>
       </c>
       <c r="E6" s="32" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F6" s="23"/>
       <c r="H6" s="3" t="s">
@@ -1748,18 +1782,8 @@
       <c r="K6" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="O6" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="P6" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="Q6" s="29"/>
-      <c r="R6" s="23" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="7" spans="2:18" x14ac:dyDescent="0.3">
+    </row>
+    <row r="7" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B7" s="3" t="s">
         <v>62</v>
       </c>
@@ -1767,7 +1791,7 @@
         <v>118</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>81</v>
+        <v>210</v>
       </c>
       <c r="E7" s="4" t="s">
         <v>119</v>
@@ -1780,23 +1804,11 @@
         <v>158</v>
       </c>
       <c r="J7" s="34" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="K7" s="4"/>
-      <c r="O7" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="P7" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="Q7" s="32" t="s">
-        <v>119</v>
-      </c>
-      <c r="R7" s="23" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="8" spans="2:18" x14ac:dyDescent="0.3">
+    </row>
+    <row r="8" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B8" s="3" t="s">
         <v>32</v>
       </c>
@@ -1817,23 +1829,11 @@
         <v>159</v>
       </c>
       <c r="J8" s="34" t="s">
-        <v>203</v>
+        <v>96</v>
       </c>
       <c r="K8" s="4"/>
-      <c r="O8" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="P8" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="Q8" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="R8" s="23" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="9" spans="2:18" x14ac:dyDescent="0.3">
+    </row>
+    <row r="9" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B9" s="3" t="s">
         <v>33</v>
       </c>
@@ -1857,20 +1857,8 @@
         <v>80</v>
       </c>
       <c r="K9" s="4"/>
-      <c r="O9" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="P9" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="Q9" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="R9" s="23" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="10" spans="2:18" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="10" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B10" s="3" t="s">
         <v>34</v>
       </c>
@@ -1881,7 +1869,7 @@
         <v>82</v>
       </c>
       <c r="E10" s="32" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F10" s="23"/>
       <c r="H10" s="5" t="s">
@@ -1891,25 +1879,13 @@
         <v>185</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="K10" s="7" t="s">
         <v>175</v>
       </c>
-      <c r="O10" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="P10" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="Q10" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="R10" s="23" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="11" spans="2:18" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="11" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B11" s="3" t="s">
         <v>126</v>
       </c>
@@ -1923,20 +1899,8 @@
         <v>119</v>
       </c>
       <c r="F11" s="23"/>
-      <c r="O11" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="P11" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="Q11" s="32" t="s">
-        <v>119</v>
-      </c>
-      <c r="R11" s="23" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="12" spans="2:18" x14ac:dyDescent="0.3">
+    </row>
+    <row r="12" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B12" s="3" t="s">
         <v>186</v>
       </c>
@@ -1958,20 +1922,8 @@
       </c>
       <c r="J12" s="36"/>
       <c r="K12" s="37"/>
-      <c r="O12" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="P12" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="Q12" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="R12" s="23" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="13" spans="2:18" x14ac:dyDescent="0.3">
+    </row>
+    <row r="13" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B13" s="25" t="s">
         <v>187</v>
       </c>
@@ -1997,20 +1949,8 @@
       <c r="K13" s="40" t="s">
         <v>108</v>
       </c>
-      <c r="O13" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="P13" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="Q13" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="R13" s="23" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="14" spans="2:18" x14ac:dyDescent="0.3">
+    </row>
+    <row r="14" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B14" s="3" t="s">
         <v>35</v>
       </c>
@@ -2034,22 +1974,10 @@
         <v>80</v>
       </c>
       <c r="K14" s="30" t="s">
-        <v>202</v>
-      </c>
-      <c r="O14" s="24" t="s">
-        <v>188</v>
-      </c>
-      <c r="P14" s="24" t="s">
-        <v>83</v>
-      </c>
-      <c r="Q14" s="26" t="s">
-        <v>119</v>
-      </c>
-      <c r="R14" s="23" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="15" spans="2:18" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="15" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B15" s="3" t="s">
         <v>134</v>
       </c>
@@ -2073,47 +2001,23 @@
         <v>80</v>
       </c>
       <c r="K15" s="31" t="s">
-        <v>202</v>
-      </c>
-      <c r="O15" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="P15" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="Q15" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="R15" s="23" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="16" spans="2:18" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="16" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B16" s="27" t="s">
         <v>108</v>
       </c>
       <c r="C16" s="28" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D16" s="28" t="s">
         <v>96</v>
       </c>
       <c r="E16" s="7"/>
       <c r="F16" s="23"/>
-      <c r="O16" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="P16" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="Q16" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="R16" s="23" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="17" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="17" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="H17" s="35" t="s">
         <v>16</v>
       </c>
@@ -2122,15 +2026,8 @@
       </c>
       <c r="J17" s="36"/>
       <c r="K17" s="37"/>
-      <c r="O17" s="28" t="s">
-        <v>200</v>
-      </c>
-      <c r="P17" s="28" t="s">
-        <v>96</v>
-      </c>
-      <c r="Q17" s="7"/>
-    </row>
-    <row r="18" spans="2:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="18" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B18" s="35" t="s">
         <v>7</v>
       </c>
@@ -2138,7 +2035,7 @@
         <v>141</v>
       </c>
       <c r="D18" s="36" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E18" s="37"/>
       <c r="H18" s="38" t="s">
@@ -2153,11 +2050,8 @@
       <c r="K18" s="40" t="s">
         <v>108</v>
       </c>
-      <c r="O18" s="19" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="19" spans="2:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="19" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B19" s="38" t="s">
         <v>55</v>
       </c>
@@ -2171,7 +2065,7 @@
         <v>108</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>42</v>
+        <v>203</v>
       </c>
       <c r="I19" s="1" t="s">
         <v>165</v>
@@ -2180,10 +2074,10 @@
         <v>80</v>
       </c>
       <c r="K19" s="30" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="20" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="20" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B20" s="3" t="s">
         <v>37</v>
       </c>
@@ -2194,10 +2088,10 @@
         <v>80</v>
       </c>
       <c r="E20" s="30" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>49</v>
+        <v>204</v>
       </c>
       <c r="I20" s="6" t="s">
         <v>169</v>
@@ -2206,12 +2100,12 @@
         <v>80</v>
       </c>
       <c r="K20" s="31" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="21" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="21" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B21" s="5" t="s">
-        <v>38</v>
+        <v>205</v>
       </c>
       <c r="C21" s="6" t="s">
         <v>109</v>
@@ -2220,11 +2114,11 @@
         <v>80</v>
       </c>
       <c r="E21" s="31" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="22" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="23" spans="2:17" x14ac:dyDescent="0.3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="22" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="23" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B23" s="35" t="s">
         <v>6</v>
       </c>
@@ -2242,7 +2136,7 @@
       <c r="J23" s="36"/>
       <c r="K23" s="37"/>
     </row>
-    <row r="24" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B24" s="38" t="s">
         <v>55</v>
       </c>
@@ -2268,7 +2162,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="25" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B25" s="3" t="s">
         <v>37</v>
       </c>
@@ -2294,7 +2188,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="26" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B26" s="3" t="s">
         <v>70</v>
       </c>
@@ -2305,10 +2199,10 @@
         <v>81</v>
       </c>
       <c r="E26" s="30" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="H26" s="5" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="I26" s="6" t="s">
         <v>181</v>
@@ -2317,10 +2211,10 @@
         <v>81</v>
       </c>
       <c r="K26" s="33" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="27" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="27" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B27" s="3" t="s">
         <v>41</v>
       </c>
@@ -2334,7 +2228,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="28" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B28" s="3" t="s">
         <v>126</v>
       </c>
@@ -2346,7 +2240,7 @@
       </c>
       <c r="E28" s="4"/>
       <c r="H28" s="35" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="I28" s="36" t="s">
         <v>105</v>
@@ -2354,7 +2248,7 @@
       <c r="J28" s="36"/>
       <c r="K28" s="37"/>
     </row>
-    <row r="29" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B29" s="3" t="s">
         <v>186</v>
       </c>
@@ -2378,7 +2272,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="30" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B30" s="5" t="s">
         <v>92</v>
       </c>
@@ -2390,7 +2284,7 @@
       </c>
       <c r="E30" s="7"/>
       <c r="H30" s="3" t="s">
-        <v>111</v>
+        <v>206</v>
       </c>
       <c r="I30" s="1" t="s">
         <v>112</v>
@@ -2402,7 +2296,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="31" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="H31" s="3" t="s">
         <v>115</v>
       </c>
@@ -2413,10 +2307,10 @@
         <v>117</v>
       </c>
       <c r="K31" s="32" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="32" spans="2:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="32" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B32" s="35" t="s">
         <v>43</v>
       </c>
@@ -2424,20 +2318,20 @@
         <v>160</v>
       </c>
       <c r="D32" s="36" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E32" s="37"/>
       <c r="H32" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="I32" s="6" t="s">
         <v>195</v>
-      </c>
-      <c r="I32" s="6" t="s">
-        <v>196</v>
       </c>
       <c r="J32" s="6" t="s">
         <v>117</v>
       </c>
       <c r="K32" s="33" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="33" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -2465,7 +2359,7 @@
         <v>80</v>
       </c>
       <c r="E34" s="30" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="H34" s="35" t="s">
         <v>120</v>
@@ -2487,7 +2381,7 @@
         <v>80</v>
       </c>
       <c r="E35" s="30" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="H35" s="38" t="s">
         <v>55</v>
@@ -2514,7 +2408,7 @@
       </c>
       <c r="E36" s="7"/>
       <c r="H36" s="3" t="s">
-        <v>124</v>
+        <v>208</v>
       </c>
       <c r="I36" s="1" t="s">
         <v>125</v>
@@ -2534,10 +2428,10 @@
         <v>113</v>
       </c>
       <c r="J37" s="1" t="s">
-        <v>81</v>
+        <v>210</v>
       </c>
       <c r="K37" s="30" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="38" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -2564,11 +2458,11 @@
       <c r="H39" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="I39" s="34" t="s">
+      <c r="I39" s="43" t="s">
         <v>132</v>
       </c>
-      <c r="J39" s="34" t="s">
-        <v>203</v>
+      <c r="J39" s="43" t="s">
+        <v>201</v>
       </c>
       <c r="K39" s="4"/>
     </row>
@@ -2589,16 +2483,16 @@
         <v>29</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="J40" s="34" t="s">
-        <v>203</v>
+        <v>96</v>
       </c>
       <c r="K40" s="4"/>
     </row>
     <row r="41" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B41" s="3" t="s">
-        <v>42</v>
+        <v>203</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>165</v>
@@ -2622,7 +2516,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="42" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B42" s="3" t="s">
         <v>46</v>
       </c>
@@ -2635,20 +2529,18 @@
       <c r="E42" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="H42" s="5" t="s">
-        <v>192</v>
-      </c>
-      <c r="I42" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="J42" s="6" t="s">
-        <v>191</v>
-      </c>
-      <c r="K42" s="7" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="H42" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I42" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="J42" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="K42" s="4"/>
+    </row>
+    <row r="43" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B43" s="3" t="s">
         <v>47</v>
       </c>
@@ -2661,8 +2553,20 @@
       <c r="E43" s="4" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="44" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H43" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="I43" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="J43" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="K43" s="7" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="44" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B44" s="3" t="s">
         <v>48</v>
       </c>
@@ -2676,7 +2580,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B45" s="3" t="s">
         <v>97</v>
       </c>
@@ -2684,17 +2588,9 @@
         <v>176</v>
       </c>
       <c r="D45" s="34" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E45" s="4"/>
-      <c r="H45" s="35" t="s">
-        <v>143</v>
-      </c>
-      <c r="I45" s="36" t="s">
-        <v>144</v>
-      </c>
-      <c r="J45" s="36"/>
-      <c r="K45" s="37"/>
     </row>
     <row r="46" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B46" s="3" t="s">
@@ -2704,23 +2600,19 @@
         <v>163</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E46" s="4" t="s">
         <v>175</v>
       </c>
-      <c r="H46" s="38" t="s">
-        <v>55</v>
-      </c>
-      <c r="I46" s="39" t="s">
-        <v>106</v>
-      </c>
-      <c r="J46" s="39" t="s">
-        <v>107</v>
-      </c>
-      <c r="K46" s="40" t="s">
-        <v>108</v>
-      </c>
+      <c r="H46" s="35" t="s">
+        <v>143</v>
+      </c>
+      <c r="I46" s="36" t="s">
+        <v>144</v>
+      </c>
+      <c r="J46" s="36"/>
+      <c r="K46" s="37"/>
     </row>
     <row r="47" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B47" s="5" t="s">
@@ -2729,35 +2621,35 @@
       <c r="C47" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="D47" s="34" t="s">
-        <v>203</v>
+      <c r="D47" s="44" t="s">
+        <v>96</v>
       </c>
       <c r="E47" s="7"/>
-      <c r="H47" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I47" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="J47" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="K47" s="29" t="s">
-        <v>110</v>
+      <c r="H47" s="38" t="s">
+        <v>55</v>
+      </c>
+      <c r="I47" s="39" t="s">
+        <v>106</v>
+      </c>
+      <c r="J47" s="39" t="s">
+        <v>107</v>
+      </c>
+      <c r="K47" s="40" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="48" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="H48" s="3" t="s">
-        <v>65</v>
+        <v>209</v>
       </c>
       <c r="I48" s="1" t="s">
-        <v>113</v>
+        <v>145</v>
       </c>
       <c r="J48" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="K48" s="30" t="s">
-        <v>202</v>
+        <v>80</v>
+      </c>
+      <c r="K48" s="29" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="49" spans="2:11" x14ac:dyDescent="0.3">
@@ -2770,15 +2662,17 @@
       <c r="D49" s="36"/>
       <c r="E49" s="37"/>
       <c r="H49" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="I49" s="34" t="s">
-        <v>148</v>
+        <v>65</v>
+      </c>
+      <c r="I49" s="1" t="s">
+        <v>113</v>
       </c>
       <c r="J49" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="K49" s="4"/>
+        <v>210</v>
+      </c>
+      <c r="K49" s="30" t="s">
+        <v>200</v>
+      </c>
     </row>
     <row r="50" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B50" s="38" t="s">
@@ -2794,21 +2688,19 @@
         <v>108</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="I50" s="1" t="s">
-        <v>149</v>
+        <v>67</v>
+      </c>
+      <c r="I50" s="34" t="s">
+        <v>148</v>
       </c>
       <c r="J50" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="K50" s="30" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="51" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+        <v>96</v>
+      </c>
+      <c r="K50" s="4"/>
+    </row>
+    <row r="51" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B51" s="3" t="s">
-        <v>182</v>
+        <v>205</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>109</v>
@@ -2817,22 +2709,22 @@
         <v>80</v>
       </c>
       <c r="E51" s="30" t="s">
-        <v>202</v>
-      </c>
-      <c r="H51" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="I51" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="J51" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="K51" s="7" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="52" spans="2:11" x14ac:dyDescent="0.3">
+        <v>200</v>
+      </c>
+      <c r="H51" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="I51" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="J51" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="K51" s="30" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="52" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B52" s="3" t="s">
         <v>52</v>
       </c>
@@ -2843,7 +2735,19 @@
         <v>80</v>
       </c>
       <c r="E52" s="30" t="s">
-        <v>202</v>
+        <v>200</v>
+      </c>
+      <c r="H52" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="I52" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="J52" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="K52" s="7" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="53" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -4765,7 +4669,7 @@
         <v>81</v>
       </c>
       <c r="E6" s="32" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F6" s="23"/>
       <c r="H6" s="3" t="s">
@@ -4879,7 +4783,7 @@
         <v>82</v>
       </c>
       <c r="E10" s="32" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F10" s="23"/>
       <c r="H10" s="5" t="s">
@@ -4889,7 +4793,7 @@
         <v>185</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="K10" s="7" t="s">
         <v>175</v>
@@ -4996,7 +4900,7 @@
         <v>80</v>
       </c>
       <c r="K14" s="30" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="R14" s="23" t="s">
         <v>189</v>
@@ -5026,7 +4930,7 @@
         <v>80</v>
       </c>
       <c r="K15" s="31" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="R15" s="23" t="s">
         <v>189</v>
@@ -5037,7 +4941,7 @@
         <v>108</v>
       </c>
       <c r="C16" s="28" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D16" s="28" t="s">
         <v>96</v>
@@ -5066,7 +4970,7 @@
         <v>141</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E18" s="12"/>
       <c r="H18" s="13" t="s">
@@ -5105,7 +5009,7 @@
         <v>80</v>
       </c>
       <c r="K19" s="30" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="20" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -5119,7 +5023,7 @@
         <v>80</v>
       </c>
       <c r="E20" s="30" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="H20" s="5" t="s">
         <v>49</v>
@@ -5131,7 +5035,7 @@
         <v>80</v>
       </c>
       <c r="K20" s="31" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="21" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -5145,7 +5049,7 @@
         <v>80</v>
       </c>
       <c r="E21" s="31" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="22" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
@@ -5230,10 +5134,10 @@
         <v>81</v>
       </c>
       <c r="E26" s="30" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="H26" s="5" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="I26" s="6" t="s">
         <v>181</v>
@@ -5242,7 +5146,7 @@
         <v>81</v>
       </c>
       <c r="K26" s="33" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="27" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -5271,7 +5175,7 @@
       </c>
       <c r="E28" s="4"/>
       <c r="H28" s="10" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="I28" s="11" t="s">
         <v>105</v>
@@ -5347,20 +5251,20 @@
         <v>160</v>
       </c>
       <c r="D32" s="11" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E32" s="12"/>
       <c r="H32" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="I32" s="6" t="s">
         <v>195</v>
-      </c>
-      <c r="I32" s="6" t="s">
-        <v>196</v>
       </c>
       <c r="J32" s="6" t="s">
         <v>117</v>
       </c>
       <c r="K32" s="33" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="33" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -5388,7 +5292,7 @@
         <v>80</v>
       </c>
       <c r="E34" s="30" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="H34" s="10" t="s">
         <v>120</v>
@@ -5410,7 +5314,7 @@
         <v>80</v>
       </c>
       <c r="E35" s="30" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="H35" s="13" t="s">
         <v>55</v>
@@ -5460,7 +5364,7 @@
         <v>81</v>
       </c>
       <c r="K37" s="30" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="38" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -5512,7 +5416,7 @@
         <v>29</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="J40" s="1" t="s">
         <v>133</v>
@@ -5559,13 +5463,13 @@
         <v>119</v>
       </c>
       <c r="H42" s="5" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="I42" s="6" t="s">
         <v>140</v>
       </c>
       <c r="J42" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="K42" s="7" t="s">
         <v>175</v>
@@ -5627,7 +5531,7 @@
         <v>163</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E46" s="4" t="s">
         <v>175</v>
@@ -5680,7 +5584,7 @@
         <v>81</v>
       </c>
       <c r="K48" s="30" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="49" spans="2:11" x14ac:dyDescent="0.3">
@@ -5726,7 +5630,7 @@
         <v>80</v>
       </c>
       <c r="K50" s="30" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="51" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -5740,7 +5644,7 @@
         <v>80</v>
       </c>
       <c r="E51" s="30" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="H51" s="5" t="s">
         <v>137</v>
@@ -5766,7 +5670,7 @@
         <v>80</v>
       </c>
       <c r="E52" s="30" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="53" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">

--- a/3_작업영역/0_테이블/테이블.xlsx
+++ b/3_작업영역/0_테이블/테이블.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Awsintel4 Repository\AwsIntel4_OWR\K_dessert\3_작업영역\0_테이블\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\awsintel4\aws4intelrepogitory\K_dessert\3_작업영역\0_테이블\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5840AAD-0FC8-4268-8EBF-85004AB6C976}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96804D3B-04CD-4254-A4FA-56A5313E0A44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{89506D57-ACF2-4766-BACF-4F8058B8758D}"/>
+    <workbookView xWindow="28815" yWindow="2895" windowWidth="21600" windowHeight="11295" xr2:uid="{89506D57-ACF2-4766-BACF-4F8058B8758D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2 (3)" sheetId="4" r:id="rId1"/>
@@ -18,26 +18,17 @@
     <sheet name="Sheet2" sheetId="2" r:id="rId3"/>
     <sheet name="Sheet2 (2)" sheetId="3" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1061" uniqueCount="211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1065" uniqueCount="213">
   <si>
     <t>index</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -869,6 +860,14 @@
   </si>
   <si>
     <t>VARCHAR2(50)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>넣은 시각</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>B_CRE_DATE</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1173,7 +1172,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1228,37 +1227,16 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1">
@@ -1274,9 +1252,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="10" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1">
@@ -1303,10 +1278,16 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="14" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1623,7 +1604,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09F92FCC-166C-4E7D-84B0-227CCB7DD483}">
-  <dimension ref="B2:K53"/>
+  <dimension ref="B2:K54"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3.25" customWidth="1"/>
@@ -1686,46 +1667,46 @@
   <sheetData>
     <row r="2" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="3" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B3" s="35" t="s">
+      <c r="B3" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="36" t="s">
+      <c r="C3" s="28" t="s">
         <v>103</v>
       </c>
-      <c r="D3" s="36"/>
-      <c r="E3" s="37"/>
-      <c r="H3" s="35" t="s">
+      <c r="D3" s="28"/>
+      <c r="E3" s="29"/>
+      <c r="H3" s="27" t="s">
         <v>152</v>
       </c>
-      <c r="I3" s="36" t="s">
+      <c r="I3" s="28" t="s">
         <v>153</v>
       </c>
-      <c r="J3" s="41"/>
-      <c r="K3" s="42"/>
+      <c r="J3" s="33"/>
+      <c r="K3" s="34"/>
     </row>
     <row r="4" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B4" s="38" t="s">
+      <c r="B4" s="30" t="s">
         <v>55</v>
       </c>
-      <c r="C4" s="39" t="s">
+      <c r="C4" s="31" t="s">
         <v>106</v>
       </c>
-      <c r="D4" s="39" t="s">
+      <c r="D4" s="31" t="s">
         <v>107</v>
       </c>
-      <c r="E4" s="40" t="s">
+      <c r="E4" s="32" t="s">
         <v>108</v>
       </c>
-      <c r="H4" s="38" t="s">
+      <c r="H4" s="30" t="s">
         <v>55</v>
       </c>
-      <c r="I4" s="39" t="s">
+      <c r="I4" s="31" t="s">
         <v>106</v>
       </c>
-      <c r="J4" s="39" t="s">
+      <c r="J4" s="31" t="s">
         <v>107</v>
       </c>
-      <c r="K4" s="40" t="s">
+      <c r="K4" s="32" t="s">
         <v>108</v>
       </c>
     </row>
@@ -1739,10 +1720,9 @@
       <c r="D5" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="E5" s="29" t="s">
+      <c r="E5" s="22" t="s">
         <v>110</v>
       </c>
-      <c r="F5" s="23"/>
       <c r="H5" s="3" t="s">
         <v>207</v>
       </c>
@@ -1752,7 +1732,7 @@
       <c r="J5" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="K5" s="29" t="s">
+      <c r="K5" s="22" t="s">
         <v>110</v>
       </c>
     </row>
@@ -1766,10 +1746,9 @@
       <c r="D6" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="E6" s="32" t="s">
+      <c r="E6" s="25" t="s">
         <v>196</v>
       </c>
-      <c r="F6" s="23"/>
       <c r="H6" s="3" t="s">
         <v>32</v>
       </c>
@@ -1796,14 +1775,13 @@
       <c r="E7" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="F7" s="23"/>
       <c r="H7" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="I7" s="34" t="s">
+      <c r="I7" t="s">
         <v>158</v>
       </c>
-      <c r="J7" s="34" t="s">
+      <c r="J7" t="s">
         <v>201</v>
       </c>
       <c r="K7" s="4"/>
@@ -1821,14 +1799,13 @@
       <c r="E8" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="F8" s="23"/>
       <c r="H8" s="3" t="s">
         <v>29</v>
       </c>
       <c r="I8" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="J8" s="34" t="s">
+      <c r="J8" t="s">
         <v>96</v>
       </c>
       <c r="K8" s="4"/>
@@ -1846,7 +1823,6 @@
       <c r="E9" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="F9" s="23"/>
       <c r="H9" s="3" t="s">
         <v>28</v>
       </c>
@@ -1868,10 +1844,9 @@
       <c r="D10" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="E10" s="32" t="s">
+      <c r="E10" s="25" t="s">
         <v>196</v>
       </c>
-      <c r="F10" s="23"/>
       <c r="H10" s="5" t="s">
         <v>162</v>
       </c>
@@ -1898,7 +1873,6 @@
       <c r="E11" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="F11" s="23"/>
     </row>
     <row r="12" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B12" s="3" t="s">
@@ -1913,40 +1887,38 @@
       <c r="E12" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="F12" s="23"/>
-      <c r="H12" s="35" t="s">
+      <c r="H12" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="I12" s="36" t="s">
+      <c r="I12" s="28" t="s">
         <v>166</v>
       </c>
-      <c r="J12" s="36"/>
-      <c r="K12" s="37"/>
+      <c r="J12" s="28"/>
+      <c r="K12" s="29"/>
     </row>
     <row r="13" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B13" s="25" t="s">
+      <c r="B13" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="C13" s="24" t="s">
+      <c r="C13" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="D13" s="24" t="s">
+      <c r="D13" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="E13" s="26" t="s">
+      <c r="E13" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="F13" s="23"/>
-      <c r="H13" s="38" t="s">
+      <c r="H13" s="30" t="s">
         <v>55</v>
       </c>
-      <c r="I13" s="39" t="s">
+      <c r="I13" s="31" t="s">
         <v>106</v>
       </c>
-      <c r="J13" s="39" t="s">
+      <c r="J13" s="31" t="s">
         <v>107</v>
       </c>
-      <c r="K13" s="40" t="s">
+      <c r="K13" s="32" t="s">
         <v>108</v>
       </c>
     </row>
@@ -1963,7 +1935,6 @@
       <c r="E14" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="F14" s="23"/>
       <c r="H14" s="3" t="s">
         <v>60</v>
       </c>
@@ -1973,7 +1944,7 @@
       <c r="J14" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="K14" s="30" t="s">
+      <c r="K14" s="23" t="s">
         <v>200</v>
       </c>
     </row>
@@ -1990,7 +1961,6 @@
       <c r="E15" s="4" t="s">
         <v>175</v>
       </c>
-      <c r="F15" s="23"/>
       <c r="H15" s="5" t="s">
         <v>61</v>
       </c>
@@ -2000,68 +1970,67 @@
       <c r="J15" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="K15" s="31" t="s">
+      <c r="K15" s="24" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="16" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B16" s="27" t="s">
+      <c r="B16" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="C16" s="28" t="s">
+      <c r="C16" s="6" t="s">
         <v>199</v>
       </c>
-      <c r="D16" s="28" t="s">
+      <c r="D16" s="6" t="s">
         <v>96</v>
       </c>
       <c r="E16" s="7"/>
-      <c r="F16" s="23"/>
     </row>
     <row r="17" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="H17" s="35" t="s">
+      <c r="H17" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="I17" s="36" t="s">
+      <c r="I17" s="28" t="s">
         <v>171</v>
       </c>
-      <c r="J17" s="36"/>
-      <c r="K17" s="37"/>
+      <c r="J17" s="28"/>
+      <c r="K17" s="29"/>
     </row>
     <row r="18" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B18" s="35" t="s">
+      <c r="B18" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="C18" s="36" t="s">
+      <c r="C18" s="28" t="s">
         <v>141</v>
       </c>
-      <c r="D18" s="36" t="s">
+      <c r="D18" s="28" t="s">
         <v>197</v>
       </c>
-      <c r="E18" s="37"/>
-      <c r="H18" s="38" t="s">
+      <c r="E18" s="29"/>
+      <c r="H18" s="30" t="s">
         <v>55</v>
       </c>
-      <c r="I18" s="39" t="s">
+      <c r="I18" s="31" t="s">
         <v>106</v>
       </c>
-      <c r="J18" s="39" t="s">
+      <c r="J18" s="31" t="s">
         <v>107</v>
       </c>
-      <c r="K18" s="40" t="s">
+      <c r="K18" s="32" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="19" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B19" s="38" t="s">
+      <c r="B19" s="30" t="s">
         <v>55</v>
       </c>
-      <c r="C19" s="39" t="s">
+      <c r="C19" s="31" t="s">
         <v>106</v>
       </c>
-      <c r="D19" s="39" t="s">
+      <c r="D19" s="31" t="s">
         <v>107</v>
       </c>
-      <c r="E19" s="40" t="s">
+      <c r="E19" s="32" t="s">
         <v>108</v>
       </c>
       <c r="H19" s="3" t="s">
@@ -2073,7 +2042,7 @@
       <c r="J19" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="K19" s="30" t="s">
+      <c r="K19" s="23" t="s">
         <v>200</v>
       </c>
     </row>
@@ -2087,7 +2056,7 @@
       <c r="D20" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="E20" s="30" t="s">
+      <c r="E20" s="23" t="s">
         <v>200</v>
       </c>
       <c r="H20" s="5" t="s">
@@ -2099,7 +2068,7 @@
       <c r="J20" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="K20" s="31" t="s">
+      <c r="K20" s="24" t="s">
         <v>200</v>
       </c>
     </row>
@@ -2113,52 +2082,52 @@
       <c r="D21" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="E21" s="31" t="s">
+      <c r="E21" s="24" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="22" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="23" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B23" s="35" t="s">
+      <c r="B23" s="27" t="s">
         <v>6</v>
       </c>
-      <c r="C23" s="36" t="s">
+      <c r="C23" s="28" t="s">
         <v>147</v>
       </c>
-      <c r="D23" s="36"/>
-      <c r="E23" s="37"/>
-      <c r="H23" s="35" t="s">
+      <c r="D23" s="28"/>
+      <c r="E23" s="29"/>
+      <c r="H23" s="27" t="s">
         <v>14</v>
       </c>
-      <c r="I23" s="36" t="s">
+      <c r="I23" s="28" t="s">
         <v>177</v>
       </c>
-      <c r="J23" s="36"/>
-      <c r="K23" s="37"/>
+      <c r="J23" s="28"/>
+      <c r="K23" s="29"/>
     </row>
     <row r="24" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B24" s="38" t="s">
+      <c r="B24" s="30" t="s">
         <v>55</v>
       </c>
-      <c r="C24" s="39" t="s">
+      <c r="C24" s="31" t="s">
         <v>106</v>
       </c>
-      <c r="D24" s="39" t="s">
+      <c r="D24" s="31" t="s">
         <v>107</v>
       </c>
-      <c r="E24" s="40" t="s">
+      <c r="E24" s="32" t="s">
         <v>108</v>
       </c>
-      <c r="H24" s="38" t="s">
+      <c r="H24" s="30" t="s">
         <v>55</v>
       </c>
-      <c r="I24" s="39" t="s">
+      <c r="I24" s="31" t="s">
         <v>106</v>
       </c>
-      <c r="J24" s="39" t="s">
+      <c r="J24" s="31" t="s">
         <v>107</v>
       </c>
-      <c r="K24" s="40" t="s">
+      <c r="K24" s="32" t="s">
         <v>108</v>
       </c>
     </row>
@@ -2172,7 +2141,7 @@
       <c r="D25" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="E25" s="29" t="s">
+      <c r="E25" s="22" t="s">
         <v>110</v>
       </c>
       <c r="H25" s="3" t="s">
@@ -2184,7 +2153,7 @@
       <c r="J25" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="K25" s="29" t="s">
+      <c r="K25" s="22" t="s">
         <v>110</v>
       </c>
     </row>
@@ -2198,7 +2167,7 @@
       <c r="D26" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="E26" s="30" t="s">
+      <c r="E26" s="23" t="s">
         <v>200</v>
       </c>
       <c r="H26" s="5" t="s">
@@ -2210,7 +2179,7 @@
       <c r="J26" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="K26" s="33" t="s">
+      <c r="K26" s="26" t="s">
         <v>196</v>
       </c>
     </row>
@@ -2239,14 +2208,14 @@
         <v>82</v>
       </c>
       <c r="E28" s="4"/>
-      <c r="H28" s="35" t="s">
+      <c r="H28" s="27" t="s">
         <v>193</v>
       </c>
-      <c r="I28" s="36" t="s">
+      <c r="I28" s="28" t="s">
         <v>105</v>
       </c>
-      <c r="J28" s="36"/>
-      <c r="K28" s="37"/>
+      <c r="J28" s="28"/>
+      <c r="K28" s="29"/>
     </row>
     <row r="29" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B29" s="3" t="s">
@@ -2259,16 +2228,16 @@
         <v>82</v>
       </c>
       <c r="E29" s="4"/>
-      <c r="H29" s="38" t="s">
+      <c r="H29" s="30" t="s">
         <v>55</v>
       </c>
-      <c r="I29" s="39" t="s">
+      <c r="I29" s="31" t="s">
         <v>106</v>
       </c>
-      <c r="J29" s="39" t="s">
+      <c r="J29" s="31" t="s">
         <v>107</v>
       </c>
-      <c r="K29" s="40" t="s">
+      <c r="K29" s="32" t="s">
         <v>108</v>
       </c>
     </row>
@@ -2292,7 +2261,7 @@
       <c r="J30" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="K30" s="29" t="s">
+      <c r="K30" s="22" t="s">
         <v>110</v>
       </c>
     </row>
@@ -2306,21 +2275,21 @@
       <c r="J31" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="K31" s="32" t="s">
+      <c r="K31" s="25" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="32" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="35" t="s">
+      <c r="B32" s="27" t="s">
         <v>43</v>
       </c>
-      <c r="C32" s="36" t="s">
+      <c r="C32" s="28" t="s">
         <v>160</v>
       </c>
-      <c r="D32" s="36" t="s">
+      <c r="D32" s="28" t="s">
         <v>197</v>
       </c>
-      <c r="E32" s="37"/>
+      <c r="E32" s="29"/>
       <c r="H32" s="5" t="s">
         <v>194</v>
       </c>
@@ -2330,21 +2299,21 @@
       <c r="J32" s="6" t="s">
         <v>117</v>
       </c>
-      <c r="K32" s="33" t="s">
+      <c r="K32" s="26" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="33" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B33" s="38" t="s">
+      <c r="B33" s="30" t="s">
         <v>55</v>
       </c>
-      <c r="C33" s="39" t="s">
+      <c r="C33" s="31" t="s">
         <v>106</v>
       </c>
-      <c r="D33" s="39" t="s">
+      <c r="D33" s="31" t="s">
         <v>107</v>
       </c>
-      <c r="E33" s="40" t="s">
+      <c r="E33" s="32" t="s">
         <v>108</v>
       </c>
     </row>
@@ -2358,17 +2327,17 @@
       <c r="D34" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="E34" s="30" t="s">
+      <c r="E34" s="23" t="s">
         <v>200</v>
       </c>
-      <c r="H34" s="35" t="s">
+      <c r="H34" s="27" t="s">
         <v>120</v>
       </c>
-      <c r="I34" s="36" t="s">
+      <c r="I34" s="28" t="s">
         <v>121</v>
       </c>
-      <c r="J34" s="36"/>
-      <c r="K34" s="37"/>
+      <c r="J34" s="28"/>
+      <c r="K34" s="29"/>
     </row>
     <row r="35" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B35" s="3" t="s">
@@ -2380,19 +2349,19 @@
       <c r="D35" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="E35" s="30" t="s">
+      <c r="E35" s="23" t="s">
         <v>200</v>
       </c>
-      <c r="H35" s="38" t="s">
+      <c r="H35" s="30" t="s">
         <v>55</v>
       </c>
-      <c r="I35" s="39" t="s">
+      <c r="I35" s="31" t="s">
         <v>106</v>
       </c>
-      <c r="J35" s="39" t="s">
+      <c r="J35" s="31" t="s">
         <v>107</v>
       </c>
-      <c r="K35" s="40" t="s">
+      <c r="K35" s="32" t="s">
         <v>108</v>
       </c>
     </row>
@@ -2416,7 +2385,7 @@
       <c r="J36" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="K36" s="29" t="s">
+      <c r="K36" s="22" t="s">
         <v>110</v>
       </c>
     </row>
@@ -2430,7 +2399,7 @@
       <c r="J37" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="K37" s="30" t="s">
+      <c r="K37" s="23" t="s">
         <v>200</v>
       </c>
     </row>
@@ -2447,36 +2416,36 @@
       <c r="K38" s="4"/>
     </row>
     <row r="39" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B39" s="35" t="s">
+      <c r="B39" s="27" t="s">
         <v>9</v>
       </c>
-      <c r="C39" s="36" t="s">
+      <c r="C39" s="28" t="s">
         <v>170</v>
       </c>
-      <c r="D39" s="36"/>
-      <c r="E39" s="37"/>
+      <c r="D39" s="28"/>
+      <c r="E39" s="29"/>
       <c r="H39" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="I39" s="43" t="s">
+      <c r="I39" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="J39" s="43" t="s">
+      <c r="J39" s="1" t="s">
         <v>201</v>
       </c>
       <c r="K39" s="4"/>
     </row>
     <row r="40" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B40" s="38" t="s">
+      <c r="B40" s="30" t="s">
         <v>55</v>
       </c>
-      <c r="C40" s="39" t="s">
+      <c r="C40" s="31" t="s">
         <v>106</v>
       </c>
-      <c r="D40" s="39" t="s">
+      <c r="D40" s="31" t="s">
         <v>107</v>
       </c>
-      <c r="E40" s="40" t="s">
+      <c r="E40" s="32" t="s">
         <v>108</v>
       </c>
       <c r="H40" s="3" t="s">
@@ -2485,7 +2454,7 @@
       <c r="I40" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="J40" s="34" t="s">
+      <c r="J40" t="s">
         <v>96</v>
       </c>
       <c r="K40" s="4"/>
@@ -2500,7 +2469,7 @@
       <c r="D41" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="E41" s="29" t="s">
+      <c r="E41" s="22" t="s">
         <v>110</v>
       </c>
       <c r="H41" s="3" t="s">
@@ -2587,7 +2556,7 @@
       <c r="C45" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="D45" s="34" t="s">
+      <c r="D45" t="s">
         <v>201</v>
       </c>
       <c r="E45" s="4"/>
@@ -2605,14 +2574,14 @@
       <c r="E46" s="4" t="s">
         <v>175</v>
       </c>
-      <c r="H46" s="35" t="s">
+      <c r="H46" s="27" t="s">
         <v>143</v>
       </c>
-      <c r="I46" s="36" t="s">
+      <c r="I46" s="28" t="s">
         <v>144</v>
       </c>
-      <c r="J46" s="36"/>
-      <c r="K46" s="37"/>
+      <c r="J46" s="28"/>
+      <c r="K46" s="29"/>
     </row>
     <row r="47" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B47" s="5" t="s">
@@ -2621,20 +2590,20 @@
       <c r="C47" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="D47" s="44" t="s">
+      <c r="D47" s="35" t="s">
         <v>96</v>
       </c>
       <c r="E47" s="7"/>
-      <c r="H47" s="38" t="s">
+      <c r="H47" s="30" t="s">
         <v>55</v>
       </c>
-      <c r="I47" s="39" t="s">
+      <c r="I47" s="31" t="s">
         <v>106</v>
       </c>
-      <c r="J47" s="39" t="s">
+      <c r="J47" s="31" t="s">
         <v>107</v>
       </c>
-      <c r="K47" s="40" t="s">
+      <c r="K47" s="32" t="s">
         <v>108</v>
       </c>
     </row>
@@ -2648,19 +2617,19 @@
       <c r="J48" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="K48" s="29" t="s">
+      <c r="K48" s="22" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="49" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B49" s="35" t="s">
+      <c r="B49" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="C49" s="36" t="s">
+      <c r="C49" s="28" t="s">
         <v>180</v>
       </c>
-      <c r="D49" s="36"/>
-      <c r="E49" s="37"/>
+      <c r="D49" s="28"/>
+      <c r="E49" s="29"/>
       <c r="H49" s="3" t="s">
         <v>65</v>
       </c>
@@ -2670,27 +2639,27 @@
       <c r="J49" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="K49" s="30" t="s">
+      <c r="K49" s="23" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="50" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B50" s="38" t="s">
+      <c r="B50" s="30" t="s">
         <v>55</v>
       </c>
-      <c r="C50" s="39" t="s">
+      <c r="C50" s="31" t="s">
         <v>106</v>
       </c>
-      <c r="D50" s="39" t="s">
+      <c r="D50" s="31" t="s">
         <v>107</v>
       </c>
-      <c r="E50" s="40" t="s">
+      <c r="E50" s="32" t="s">
         <v>108</v>
       </c>
       <c r="H50" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="I50" s="34" t="s">
+      <c r="I50" t="s">
         <v>148</v>
       </c>
       <c r="J50" s="1" t="s">
@@ -2708,7 +2677,7 @@
       <c r="D51" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="E51" s="30" t="s">
+      <c r="E51" s="23" t="s">
         <v>200</v>
       </c>
       <c r="H51" s="3" t="s">
@@ -2720,7 +2689,7 @@
       <c r="J51" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="K51" s="30" t="s">
+      <c r="K51" s="23" t="s">
         <v>200</v>
       </c>
     </row>
@@ -2734,7 +2703,7 @@
       <c r="D52" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="E52" s="30" t="s">
+      <c r="E52" s="23" t="s">
         <v>200</v>
       </c>
       <c r="H52" s="5" t="s">
@@ -2750,17 +2719,31 @@
         <v>131</v>
       </c>
     </row>
-    <row r="53" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B53" s="5" t="s">
+    <row r="53" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B53" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="C53" s="6" t="s">
+      <c r="C53" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="D53" s="6" t="s">
+      <c r="D53" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="E53" s="7"/>
+      <c r="E53" s="4"/>
+    </row>
+    <row r="54" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B54" s="36" t="s">
+        <v>211</v>
+      </c>
+      <c r="C54" s="37" t="s">
+        <v>212</v>
+      </c>
+      <c r="D54" s="37" t="s">
+        <v>83</v>
+      </c>
+      <c r="E54" s="38" t="s">
+        <v>131</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -3362,7 +3345,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87580854-C28E-4E95-AB15-75B01A5EA365}">
-  <dimension ref="B2:L53"/>
+  <dimension ref="B2:K53"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3.25" customWidth="1"/>
@@ -3422,8 +3405,8 @@
     <col min="72" max="72" width="7.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="3" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="3" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B3" s="10" t="s">
         <v>8</v>
       </c>
@@ -3442,7 +3425,7 @@
       <c r="J3" s="11"/>
       <c r="K3" s="12"/>
     </row>
-    <row r="4" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B4" s="13" t="s">
         <v>55</v>
       </c>
@@ -3469,7 +3452,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B5" s="3" t="s">
         <v>182</v>
       </c>
@@ -3482,7 +3465,6 @@
       <c r="E5" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="F5" s="23"/>
       <c r="H5" s="3" t="s">
         <v>111</v>
       </c>
@@ -3495,9 +3477,8 @@
       <c r="K5" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="L5" s="23"/>
-    </row>
-    <row r="6" spans="2:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="6" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B6" s="3" t="s">
         <v>68</v>
       </c>
@@ -3510,7 +3491,6 @@
       <c r="E6" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="F6" s="23"/>
       <c r="H6" s="5" t="s">
         <v>115</v>
       </c>
@@ -3522,7 +3502,7 @@
       </c>
       <c r="K6" s="7"/>
     </row>
-    <row r="7" spans="2:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B7" s="3" t="s">
         <v>62</v>
       </c>
@@ -3535,10 +3515,9 @@
       <c r="E7" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="F7" s="23"/>
       <c r="G7" s="8"/>
     </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B8" s="3" t="s">
         <v>32</v>
       </c>
@@ -3551,7 +3530,6 @@
       <c r="E8" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="F8" s="23"/>
       <c r="H8" s="10" t="s">
         <v>120</v>
       </c>
@@ -3561,7 +3539,7 @@
       <c r="J8" s="11"/>
       <c r="K8" s="12"/>
     </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B9" s="3" t="s">
         <v>33</v>
       </c>
@@ -3574,7 +3552,6 @@
       <c r="E9" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="F9" s="23"/>
       <c r="H9" s="13" t="s">
         <v>55</v>
       </c>
@@ -3588,7 +3565,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B10" s="3" t="s">
         <v>34</v>
       </c>
@@ -3601,7 +3578,6 @@
       <c r="E10" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="F10" s="23"/>
       <c r="H10" s="3" t="s">
         <v>124</v>
       </c>
@@ -3614,9 +3590,8 @@
       <c r="K10" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="L10" s="23"/>
-    </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="11" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B11" s="3" t="s">
         <v>126</v>
       </c>
@@ -3629,7 +3604,6 @@
       <c r="E11" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="F11" s="23"/>
       <c r="H11" s="3" t="s">
         <v>65</v>
       </c>
@@ -3642,9 +3616,8 @@
       <c r="K11" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="L11" s="23"/>
-    </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="12" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B12" s="3" t="s">
         <v>186</v>
       </c>
@@ -3657,7 +3630,6 @@
       <c r="E12" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="F12" s="23"/>
       <c r="H12" s="3" t="s">
         <v>66</v>
       </c>
@@ -3668,9 +3640,8 @@
         <v>184</v>
       </c>
       <c r="K12" s="4"/>
-      <c r="L12" s="23"/>
-    </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="13" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B13" s="18" t="s">
         <v>187</v>
       </c>
@@ -3683,7 +3654,6 @@
       <c r="E13" s="20" t="s">
         <v>119</v>
       </c>
-      <c r="F13" s="23"/>
       <c r="H13" s="3" t="s">
         <v>67</v>
       </c>
@@ -3694,9 +3664,8 @@
         <v>133</v>
       </c>
       <c r="K13" s="4"/>
-      <c r="L13" s="23"/>
-    </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="14" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B14" s="3" t="s">
         <v>35</v>
       </c>
@@ -3709,7 +3678,6 @@
       <c r="E14" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="F14" s="23"/>
       <c r="H14" s="3" t="s">
         <v>137</v>
       </c>
@@ -3722,9 +3690,8 @@
       <c r="K14" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="L14" s="23"/>
-    </row>
-    <row r="15" spans="2:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="15" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B15" s="5" t="s">
         <v>134</v>
       </c>
@@ -3735,7 +3702,6 @@
         <v>136</v>
       </c>
       <c r="E15" s="7"/>
-      <c r="F15" s="22"/>
       <c r="H15" s="5" t="s">
         <v>139</v>
       </c>
@@ -3747,8 +3713,8 @@
       </c>
       <c r="K15" s="7"/>
     </row>
-    <row r="16" spans="2:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="17" spans="2:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="17" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B17" s="10" t="s">
         <v>7</v>
       </c>
@@ -3759,7 +3725,7 @@
       <c r="E17" s="12"/>
       <c r="F17" s="21"/>
     </row>
-    <row r="18" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B18" s="13" t="s">
         <v>55</v>
       </c>
@@ -3782,7 +3748,7 @@
       <c r="J18" s="11"/>
       <c r="K18" s="12"/>
     </row>
-    <row r="19" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B19" s="3" t="s">
         <v>37</v>
       </c>
@@ -3795,7 +3761,6 @@
       <c r="E19" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="F19" s="23"/>
       <c r="H19" s="13" t="s">
         <v>55</v>
       </c>
@@ -3809,7 +3774,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="20" spans="2:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B20" s="5" t="s">
         <v>38</v>
       </c>
@@ -3836,9 +3801,8 @@
       <c r="K20" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="L20" s="23"/>
-    </row>
-    <row r="21" spans="2:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="21" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="H21" s="3" t="s">
         <v>65</v>
       </c>
@@ -3851,9 +3815,8 @@
       <c r="K21" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="L21" s="23"/>
-    </row>
-    <row r="22" spans="2:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="22" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B22" s="10" t="s">
         <v>6</v>
       </c>
@@ -3873,9 +3836,8 @@
         <v>96</v>
       </c>
       <c r="K22" s="4"/>
-      <c r="L22" s="23"/>
-    </row>
-    <row r="23" spans="2:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="23" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B23" s="13" t="s">
         <v>55</v>
       </c>
@@ -3901,9 +3863,8 @@
       <c r="K23" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="L23" s="23"/>
-    </row>
-    <row r="24" spans="2:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="24" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B24" s="3" t="s">
         <v>37</v>
       </c>
@@ -3916,7 +3877,6 @@
       <c r="E24" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="F24" s="23"/>
       <c r="H24" s="5" t="s">
         <v>137</v>
       </c>
@@ -3930,7 +3890,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="25" spans="2:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B25" s="3" t="s">
         <v>70</v>
       </c>
@@ -3943,9 +3903,8 @@
       <c r="E25" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="F25" s="23"/>
-    </row>
-    <row r="26" spans="2:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="26" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B26" s="3" t="s">
         <v>41</v>
       </c>
@@ -3958,7 +3917,6 @@
       <c r="E26" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="F26" s="23"/>
       <c r="H26" s="10" t="s">
         <v>152</v>
       </c>
@@ -3968,7 +3926,7 @@
       <c r="J26" s="16"/>
       <c r="K26" s="17"/>
     </row>
-    <row r="27" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B27" s="3" t="s">
         <v>126</v>
       </c>
@@ -3981,7 +3939,6 @@
       <c r="E27" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="F27" s="23"/>
       <c r="H27" s="13" t="s">
         <v>55</v>
       </c>
@@ -3995,7 +3952,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="28" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B28" s="3" t="s">
         <v>186</v>
       </c>
@@ -4008,7 +3965,6 @@
       <c r="E28" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="F28" s="23"/>
       <c r="H28" s="3" t="s">
         <v>154</v>
       </c>
@@ -4021,9 +3977,8 @@
       <c r="K28" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="L28" s="23"/>
-    </row>
-    <row r="29" spans="2:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="29" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B29" s="3" t="s">
         <v>92</v>
       </c>
@@ -4036,7 +3991,6 @@
       <c r="E29" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="F29" s="23"/>
       <c r="H29" s="3" t="s">
         <v>32</v>
       </c>
@@ -4047,9 +4001,8 @@
         <v>184</v>
       </c>
       <c r="K29" s="4"/>
-      <c r="L29" s="23"/>
-    </row>
-    <row r="30" spans="2:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="30" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B30" s="5" t="s">
         <v>94</v>
       </c>
@@ -4060,7 +4013,6 @@
         <v>96</v>
       </c>
       <c r="E30" s="7"/>
-      <c r="F30" s="22"/>
       <c r="H30" s="3" t="s">
         <v>55</v>
       </c>
@@ -4071,9 +4023,8 @@
         <v>133</v>
       </c>
       <c r="K30" s="4"/>
-      <c r="L30" s="23"/>
-    </row>
-    <row r="31" spans="2:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="31" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="G31" s="9"/>
       <c r="H31" s="3" t="s">
         <v>29</v>
@@ -4085,9 +4036,8 @@
         <v>133</v>
       </c>
       <c r="K31" s="4"/>
-      <c r="L31" s="23"/>
-    </row>
-    <row r="32" spans="2:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="32" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B32" s="10" t="s">
         <v>43</v>
       </c>
@@ -4107,9 +4057,8 @@
         <v>80</v>
       </c>
       <c r="K32" s="4"/>
-      <c r="L32" s="23"/>
-    </row>
-    <row r="33" spans="2:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="33" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B33" s="13" t="s">
         <v>55</v>
       </c>
@@ -4136,7 +4085,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="34" spans="2:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B34" s="3" t="s">
         <v>37</v>
       </c>
@@ -4149,9 +4098,8 @@
       <c r="E34" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="F34" s="23"/>
-    </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="35" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B35" s="3" t="s">
         <v>44</v>
       </c>
@@ -4164,7 +4112,6 @@
       <c r="E35" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="F35" s="23"/>
       <c r="H35" s="10" t="s">
         <v>27</v>
       </c>
@@ -4174,7 +4121,7 @@
       <c r="J35" s="11"/>
       <c r="K35" s="12"/>
     </row>
-    <row r="36" spans="2:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B36" s="5" t="s">
         <v>167</v>
       </c>
@@ -4185,7 +4132,6 @@
         <v>100</v>
       </c>
       <c r="E36" s="7"/>
-      <c r="F36" s="22"/>
       <c r="H36" s="13" t="s">
         <v>55</v>
       </c>
@@ -4199,7 +4145,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:11" x14ac:dyDescent="0.3">
       <c r="H37" s="3" t="s">
         <v>60</v>
       </c>
@@ -4212,9 +4158,8 @@
       <c r="K37" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="L37" s="23"/>
-    </row>
-    <row r="38" spans="2:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="38" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="H38" s="5" t="s">
         <v>61</v>
       </c>
@@ -4227,9 +4172,8 @@
       <c r="K38" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="L38" s="23"/>
-    </row>
-    <row r="39" spans="2:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="39" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B39" s="10" t="s">
         <v>9</v>
       </c>
@@ -4240,7 +4184,7 @@
       <c r="E39" s="12"/>
       <c r="F39" s="21"/>
     </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B40" s="13" t="s">
         <v>55</v>
       </c>
@@ -4263,7 +4207,7 @@
       <c r="J40" s="11"/>
       <c r="K40" s="12"/>
     </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B41" s="3" t="s">
         <v>42</v>
       </c>
@@ -4276,7 +4220,6 @@
       <c r="E41" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="F41" s="23"/>
       <c r="H41" s="13" t="s">
         <v>55</v>
       </c>
@@ -4290,7 +4233,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B42" s="3" t="s">
         <v>46</v>
       </c>
@@ -4303,7 +4246,6 @@
       <c r="E42" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="F42" s="23"/>
       <c r="H42" s="3" t="s">
         <v>42</v>
       </c>
@@ -4316,9 +4258,8 @@
       <c r="K42" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="L42" s="23"/>
-    </row>
-    <row r="43" spans="2:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="43" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B43" s="3" t="s">
         <v>47</v>
       </c>
@@ -4331,7 +4272,6 @@
       <c r="E43" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="F43" s="23"/>
       <c r="H43" s="5" t="s">
         <v>49</v>
       </c>
@@ -4345,7 +4285,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B44" s="3" t="s">
         <v>48</v>
       </c>
@@ -4358,9 +4298,8 @@
       <c r="E44" s="4" t="s">
         <v>175</v>
       </c>
-      <c r="F44" s="23"/>
-    </row>
-    <row r="45" spans="2:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="45" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B45" s="3" t="s">
         <v>97</v>
       </c>
@@ -4371,9 +4310,8 @@
         <v>133</v>
       </c>
       <c r="E45" s="4"/>
-      <c r="F45" s="23"/>
-    </row>
-    <row r="46" spans="2:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="46" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B46" s="3" t="s">
         <v>162</v>
       </c>
@@ -4386,7 +4324,6 @@
       <c r="E46" s="4" t="s">
         <v>164</v>
       </c>
-      <c r="F46" s="23"/>
       <c r="H46" s="10" t="s">
         <v>14</v>
       </c>
@@ -4396,7 +4333,7 @@
       <c r="J46" s="11"/>
       <c r="K46" s="12"/>
     </row>
-    <row r="47" spans="2:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B47" s="5" t="s">
         <v>178</v>
       </c>
@@ -4407,7 +4344,6 @@
         <v>133</v>
       </c>
       <c r="E47" s="7"/>
-      <c r="F47" s="22"/>
       <c r="H47" s="13" t="s">
         <v>55</v>
       </c>
@@ -4421,7 +4357,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="48" spans="2:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="H48" s="3" t="s">
         <v>50</v>
       </c>
@@ -4486,7 +4422,6 @@
       <c r="E51" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="F51" s="23"/>
     </row>
     <row r="52" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B52" s="3" t="s">
@@ -4501,7 +4436,6 @@
       <c r="E52" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="F52" s="23"/>
     </row>
     <row r="53" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B53" s="5" t="s">
@@ -4514,7 +4448,6 @@
         <v>100</v>
       </c>
       <c r="E53" s="7"/>
-      <c r="F53" s="22"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -4641,10 +4574,9 @@
       <c r="D5" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="E5" s="29" t="s">
+      <c r="E5" s="22" t="s">
         <v>110</v>
       </c>
-      <c r="F5" s="23"/>
       <c r="H5" s="3" t="s">
         <v>154</v>
       </c>
@@ -4654,7 +4586,7 @@
       <c r="J5" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="K5" s="29" t="s">
+      <c r="K5" s="22" t="s">
         <v>110</v>
       </c>
     </row>
@@ -4668,10 +4600,9 @@
       <c r="D6" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="E6" s="32" t="s">
+      <c r="E6" s="25" t="s">
         <v>196</v>
       </c>
-      <c r="F6" s="23"/>
       <c r="H6" s="3" t="s">
         <v>32</v>
       </c>
@@ -4684,7 +4615,7 @@
       <c r="K6" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="R6" s="23" t="s">
+      <c r="R6" t="s">
         <v>189</v>
       </c>
     </row>
@@ -4701,7 +4632,6 @@
       <c r="E7" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="F7" s="23"/>
       <c r="H7" s="3" t="s">
         <v>55</v>
       </c>
@@ -4712,7 +4642,7 @@
         <v>133</v>
       </c>
       <c r="K7" s="4"/>
-      <c r="R7" s="23" t="s">
+      <c r="R7" t="s">
         <v>189</v>
       </c>
     </row>
@@ -4729,7 +4659,6 @@
       <c r="E8" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="F8" s="23"/>
       <c r="H8" s="3" t="s">
         <v>29</v>
       </c>
@@ -4740,7 +4669,7 @@
         <v>133</v>
       </c>
       <c r="K8" s="4"/>
-      <c r="R8" s="23" t="s">
+      <c r="R8" t="s">
         <v>189</v>
       </c>
     </row>
@@ -4757,7 +4686,6 @@
       <c r="E9" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="F9" s="23"/>
       <c r="H9" s="3" t="s">
         <v>28</v>
       </c>
@@ -4768,7 +4696,7 @@
         <v>80</v>
       </c>
       <c r="K9" s="4"/>
-      <c r="R9" s="23" t="s">
+      <c r="R9" t="s">
         <v>189</v>
       </c>
     </row>
@@ -4782,10 +4710,9 @@
       <c r="D10" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="E10" s="32" t="s">
+      <c r="E10" s="25" t="s">
         <v>196</v>
       </c>
-      <c r="F10" s="23"/>
       <c r="H10" s="5" t="s">
         <v>162</v>
       </c>
@@ -4798,7 +4725,7 @@
       <c r="K10" s="7" t="s">
         <v>175</v>
       </c>
-      <c r="R10" s="23" t="s">
+      <c r="R10" t="s">
         <v>189</v>
       </c>
     </row>
@@ -4815,8 +4742,7 @@
       <c r="E11" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="F11" s="23"/>
-      <c r="R11" s="23" t="s">
+      <c r="R11" t="s">
         <v>189</v>
       </c>
     </row>
@@ -4833,7 +4759,6 @@
       <c r="E12" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="F12" s="23"/>
       <c r="H12" s="10" t="s">
         <v>27</v>
       </c>
@@ -4842,24 +4767,23 @@
       </c>
       <c r="J12" s="11"/>
       <c r="K12" s="12"/>
-      <c r="R12" s="23" t="s">
+      <c r="R12" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="13" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B13" s="25" t="s">
+      <c r="B13" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="C13" s="24" t="s">
+      <c r="C13" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="D13" s="24" t="s">
+      <c r="D13" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="E13" s="26" t="s">
+      <c r="E13" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="F13" s="23"/>
       <c r="H13" s="13" t="s">
         <v>55</v>
       </c>
@@ -4872,7 +4796,7 @@
       <c r="K13" s="15" t="s">
         <v>108</v>
       </c>
-      <c r="R13" s="23" t="s">
+      <c r="R13" t="s">
         <v>189</v>
       </c>
     </row>
@@ -4889,7 +4813,6 @@
       <c r="E14" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="F14" s="23"/>
       <c r="H14" s="3" t="s">
         <v>60</v>
       </c>
@@ -4899,10 +4822,10 @@
       <c r="J14" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="K14" s="30" t="s">
+      <c r="K14" s="23" t="s">
         <v>200</v>
       </c>
-      <c r="R14" s="23" t="s">
+      <c r="R14" t="s">
         <v>189</v>
       </c>
     </row>
@@ -4919,7 +4842,6 @@
       <c r="E15" s="4" t="s">
         <v>175</v>
       </c>
-      <c r="F15" s="23"/>
       <c r="H15" s="5" t="s">
         <v>61</v>
       </c>
@@ -4929,26 +4851,25 @@
       <c r="J15" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="K15" s="31" t="s">
+      <c r="K15" s="24" t="s">
         <v>200</v>
       </c>
-      <c r="R15" s="23" t="s">
+      <c r="R15" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="16" spans="2:18" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B16" s="27" t="s">
+      <c r="B16" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="C16" s="28" t="s">
+      <c r="C16" s="6" t="s">
         <v>199</v>
       </c>
-      <c r="D16" s="28" t="s">
+      <c r="D16" s="6" t="s">
         <v>96</v>
       </c>
       <c r="E16" s="7"/>
-      <c r="F16" s="23"/>
-      <c r="R16" s="23" t="s">
+      <c r="R16" t="s">
         <v>189</v>
       </c>
     </row>
@@ -5008,7 +4929,7 @@
       <c r="J19" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="K19" s="30" t="s">
+      <c r="K19" s="23" t="s">
         <v>200</v>
       </c>
     </row>
@@ -5022,7 +4943,7 @@
       <c r="D20" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="E20" s="30" t="s">
+      <c r="E20" s="23" t="s">
         <v>200</v>
       </c>
       <c r="H20" s="5" t="s">
@@ -5034,7 +4955,7 @@
       <c r="J20" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="K20" s="31" t="s">
+      <c r="K20" s="24" t="s">
         <v>200</v>
       </c>
     </row>
@@ -5048,7 +4969,7 @@
       <c r="D21" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="E21" s="31" t="s">
+      <c r="E21" s="24" t="s">
         <v>200</v>
       </c>
     </row>
@@ -5107,7 +5028,7 @@
       <c r="D25" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="E25" s="29" t="s">
+      <c r="E25" s="22" t="s">
         <v>110</v>
       </c>
       <c r="H25" s="3" t="s">
@@ -5119,7 +5040,7 @@
       <c r="J25" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="K25" s="29" t="s">
+      <c r="K25" s="22" t="s">
         <v>110</v>
       </c>
     </row>
@@ -5133,7 +5054,7 @@
       <c r="D26" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="E26" s="30" t="s">
+      <c r="E26" s="23" t="s">
         <v>200</v>
       </c>
       <c r="H26" s="5" t="s">
@@ -5145,7 +5066,7 @@
       <c r="J26" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="K26" s="33" t="s">
+      <c r="K26" s="26" t="s">
         <v>196</v>
       </c>
     </row>
@@ -5227,7 +5148,7 @@
       <c r="J30" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="K30" s="29" t="s">
+      <c r="K30" s="22" t="s">
         <v>110</v>
       </c>
     </row>
@@ -5263,7 +5184,7 @@
       <c r="J32" s="6" t="s">
         <v>117</v>
       </c>
-      <c r="K32" s="33" t="s">
+      <c r="K32" s="26" t="s">
         <v>196</v>
       </c>
     </row>
@@ -5291,7 +5212,7 @@
       <c r="D34" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="E34" s="30" t="s">
+      <c r="E34" s="23" t="s">
         <v>200</v>
       </c>
       <c r="H34" s="10" t="s">
@@ -5313,7 +5234,7 @@
       <c r="D35" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="E35" s="30" t="s">
+      <c r="E35" s="23" t="s">
         <v>200</v>
       </c>
       <c r="H35" s="13" t="s">
@@ -5349,7 +5270,7 @@
       <c r="J36" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="K36" s="29" t="s">
+      <c r="K36" s="22" t="s">
         <v>110</v>
       </c>
     </row>
@@ -5363,7 +5284,7 @@
       <c r="J37" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="K37" s="30" t="s">
+      <c r="K37" s="23" t="s">
         <v>200</v>
       </c>
     </row>
@@ -5433,7 +5354,7 @@
       <c r="D41" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="E41" s="29" t="s">
+      <c r="E41" s="22" t="s">
         <v>110</v>
       </c>
       <c r="H41" s="3" t="s">
@@ -5569,7 +5490,7 @@
       <c r="J47" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="K47" s="29" t="s">
+      <c r="K47" s="22" t="s">
         <v>110</v>
       </c>
     </row>
@@ -5583,7 +5504,7 @@
       <c r="J48" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="K48" s="30" t="s">
+      <c r="K48" s="23" t="s">
         <v>200</v>
       </c>
     </row>
@@ -5629,7 +5550,7 @@
       <c r="J50" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="K50" s="30" t="s">
+      <c r="K50" s="23" t="s">
         <v>200</v>
       </c>
     </row>
@@ -5643,7 +5564,7 @@
       <c r="D51" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="E51" s="30" t="s">
+      <c r="E51" s="23" t="s">
         <v>200</v>
       </c>
       <c r="H51" s="5" t="s">
@@ -5669,7 +5590,7 @@
       <c r="D52" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="E52" s="30" t="s">
+      <c r="E52" s="23" t="s">
         <v>200</v>
       </c>
     </row>

--- a/3_작업영역/0_테이블/테이블.xlsx
+++ b/3_작업영역/0_테이블/테이블.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\awsintel4\aws4intelrepogitory\K_dessert\3_작업영역\0_테이블\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Awsintel4 Repository\AwsIntel4_OWR\K_dessert\3_작업영역\0_테이블\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96804D3B-04CD-4254-A4FA-56A5313E0A44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6C152E3-66DC-4354-B04C-63104479EE2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28815" yWindow="2895" windowWidth="21600" windowHeight="11295" xr2:uid="{89506D57-ACF2-4766-BACF-4F8058B8758D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{89506D57-ACF2-4766-BACF-4F8058B8758D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2 (3)" sheetId="4" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1065" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1068" uniqueCount="216">
   <si>
     <t>index</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -868,6 +868,18 @@
   </si>
   <si>
     <t>B_CRE_DATE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>관리자여부</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M_ADMIN</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NUMBER(1)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1172,7 +1184,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1288,6 +1300,15 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1604,7 +1625,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09F92FCC-166C-4E7D-84B0-227CCB7DD483}">
-  <dimension ref="B2:K54"/>
+  <dimension ref="B2:K55"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3.25" customWidth="1"/>
@@ -1975,18 +1996,28 @@
       </c>
     </row>
     <row r="16" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="39" t="s">
+        <v>213</v>
+      </c>
+      <c r="C16" s="40" t="s">
+        <v>214</v>
+      </c>
+      <c r="D16" s="40" t="s">
+        <v>215</v>
+      </c>
+      <c r="E16" s="41"/>
+    </row>
+    <row r="17" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B17" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="C17" s="6" t="s">
         <v>199</v>
       </c>
-      <c r="D16" s="6" t="s">
+      <c r="D17" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="E16" s="7"/>
-    </row>
-    <row r="17" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E17" s="7"/>
       <c r="H17" s="27" t="s">
         <v>16</v>
       </c>
@@ -1996,17 +2027,7 @@
       <c r="J17" s="28"/>
       <c r="K17" s="29"/>
     </row>
-    <row r="18" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B18" s="27" t="s">
-        <v>7</v>
-      </c>
-      <c r="C18" s="28" t="s">
-        <v>141</v>
-      </c>
-      <c r="D18" s="28" t="s">
-        <v>197</v>
-      </c>
-      <c r="E18" s="29"/>
+    <row r="18" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="H18" s="30" t="s">
         <v>55</v>
       </c>
@@ -2021,18 +2042,16 @@
       </c>
     </row>
     <row r="19" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B19" s="30" t="s">
-        <v>55</v>
-      </c>
-      <c r="C19" s="31" t="s">
-        <v>106</v>
-      </c>
-      <c r="D19" s="31" t="s">
-        <v>107</v>
-      </c>
-      <c r="E19" s="32" t="s">
-        <v>108</v>
-      </c>
+      <c r="B19" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" s="28" t="s">
+        <v>141</v>
+      </c>
+      <c r="D19" s="28" t="s">
+        <v>197</v>
+      </c>
+      <c r="E19" s="29"/>
       <c r="H19" s="3" t="s">
         <v>203</v>
       </c>
@@ -2047,17 +2066,17 @@
       </c>
     </row>
     <row r="20" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B20" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="E20" s="23" t="s">
-        <v>200</v>
+      <c r="B20" s="30" t="s">
+        <v>55</v>
+      </c>
+      <c r="C20" s="31" t="s">
+        <v>106</v>
+      </c>
+      <c r="D20" s="31" t="s">
+        <v>107</v>
+      </c>
+      <c r="E20" s="32" t="s">
+        <v>108</v>
       </c>
       <c r="H20" s="5" t="s">
         <v>204</v>
@@ -2072,30 +2091,35 @@
         <v>200</v>
       </c>
     </row>
-    <row r="21" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B21" s="5" t="s">
+    <row r="21" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B21" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="E21" s="23" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="22" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B22" s="5" t="s">
         <v>205</v>
       </c>
-      <c r="C21" s="6" t="s">
+      <c r="C22" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="D21" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="E21" s="24" t="s">
+      <c r="D22" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="E22" s="24" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="22" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="23" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B23" s="27" t="s">
-        <v>6</v>
-      </c>
-      <c r="C23" s="28" t="s">
-        <v>147</v>
-      </c>
-      <c r="D23" s="28"/>
-      <c r="E23" s="29"/>
+    <row r="23" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="H23" s="27" t="s">
         <v>14</v>
       </c>
@@ -2106,18 +2130,14 @@
       <c r="K23" s="29"/>
     </row>
     <row r="24" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B24" s="30" t="s">
-        <v>55</v>
-      </c>
-      <c r="C24" s="31" t="s">
-        <v>106</v>
-      </c>
-      <c r="D24" s="31" t="s">
-        <v>107</v>
-      </c>
-      <c r="E24" s="32" t="s">
-        <v>108</v>
-      </c>
+      <c r="B24" s="27" t="s">
+        <v>6</v>
+      </c>
+      <c r="C24" s="28" t="s">
+        <v>147</v>
+      </c>
+      <c r="D24" s="28"/>
+      <c r="E24" s="29"/>
       <c r="H24" s="30" t="s">
         <v>55</v>
       </c>
@@ -2132,17 +2152,17 @@
       </c>
     </row>
     <row r="25" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B25" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="E25" s="22" t="s">
-        <v>110</v>
+      <c r="B25" s="30" t="s">
+        <v>55</v>
+      </c>
+      <c r="C25" s="31" t="s">
+        <v>106</v>
+      </c>
+      <c r="D25" s="31" t="s">
+        <v>107</v>
+      </c>
+      <c r="E25" s="32" t="s">
+        <v>108</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>50</v>
@@ -2159,16 +2179,16 @@
     </row>
     <row r="26" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B26" s="3" t="s">
-        <v>70</v>
+        <v>37</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>116</v>
+        <v>142</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="E26" s="23" t="s">
-        <v>200</v>
+        <v>80</v>
+      </c>
+      <c r="E26" s="22" t="s">
+        <v>110</v>
       </c>
       <c r="H26" s="5" t="s">
         <v>198</v>
@@ -2185,29 +2205,31 @@
     </row>
     <row r="27" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B27" s="3" t="s">
-        <v>41</v>
+        <v>70</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>151</v>
+        <v>116</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="E27" s="4" t="s">
-        <v>131</v>
+        <v>81</v>
+      </c>
+      <c r="E27" s="23" t="s">
+        <v>200</v>
       </c>
     </row>
     <row r="28" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B28" s="3" t="s">
-        <v>126</v>
+        <v>41</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>127</v>
+        <v>151</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="E28" s="4"/>
+        <v>83</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>131</v>
+      </c>
       <c r="H28" s="27" t="s">
         <v>193</v>
       </c>
@@ -2219,10 +2241,10 @@
     </row>
     <row r="29" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B29" s="3" t="s">
-        <v>186</v>
+        <v>126</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>82</v>
@@ -2241,17 +2263,17 @@
         <v>108</v>
       </c>
     </row>
-    <row r="30" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B30" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="C30" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="D30" s="6" t="s">
+    <row r="30" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B30" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="D30" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="E30" s="7"/>
+      <c r="E30" s="4"/>
       <c r="H30" s="3" t="s">
         <v>206</v>
       </c>
@@ -2266,6 +2288,16 @@
       </c>
     </row>
     <row r="31" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B31" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="D31" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="E31" s="7"/>
       <c r="H31" s="3" t="s">
         <v>115</v>
       </c>
@@ -2280,16 +2312,6 @@
       </c>
     </row>
     <row r="32" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="27" t="s">
-        <v>43</v>
-      </c>
-      <c r="C32" s="28" t="s">
-        <v>160</v>
-      </c>
-      <c r="D32" s="28" t="s">
-        <v>197</v>
-      </c>
-      <c r="E32" s="29"/>
       <c r="H32" s="5" t="s">
         <v>194</v>
       </c>
@@ -2304,31 +2326,29 @@
       </c>
     </row>
     <row r="33" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B33" s="30" t="s">
+      <c r="B33" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="C33" s="28" t="s">
+        <v>160</v>
+      </c>
+      <c r="D33" s="28" t="s">
+        <v>197</v>
+      </c>
+      <c r="E33" s="29"/>
+    </row>
+    <row r="34" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B34" s="30" t="s">
         <v>55</v>
       </c>
-      <c r="C33" s="31" t="s">
+      <c r="C34" s="31" t="s">
         <v>106</v>
       </c>
-      <c r="D33" s="31" t="s">
+      <c r="D34" s="31" t="s">
         <v>107</v>
       </c>
-      <c r="E33" s="32" t="s">
+      <c r="E34" s="32" t="s">
         <v>108</v>
-      </c>
-    </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B34" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="E34" s="23" t="s">
-        <v>200</v>
       </c>
       <c r="H34" s="27" t="s">
         <v>120</v>
@@ -2341,10 +2361,10 @@
     </row>
     <row r="35" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B35" s="3" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>165</v>
+        <v>142</v>
       </c>
       <c r="D35" s="1" t="s">
         <v>80</v>
@@ -2365,17 +2385,19 @@
         <v>108</v>
       </c>
     </row>
-    <row r="36" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B36" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="C36" s="6" t="s">
-        <v>168</v>
-      </c>
-      <c r="D36" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="E36" s="7"/>
+    <row r="36" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B36" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="E36" s="23" t="s">
+        <v>200</v>
+      </c>
       <c r="H36" s="3" t="s">
         <v>208</v>
       </c>
@@ -2389,7 +2411,17 @@
         <v>110</v>
       </c>
     </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B37" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="C37" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="D37" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="E37" s="7"/>
       <c r="H37" s="3" t="s">
         <v>65</v>
       </c>
@@ -2403,7 +2435,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="38" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:11" x14ac:dyDescent="0.3">
       <c r="H38" s="3" t="s">
         <v>66</v>
       </c>
@@ -2415,15 +2447,7 @@
       </c>
       <c r="K38" s="4"/>
     </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B39" s="27" t="s">
-        <v>9</v>
-      </c>
-      <c r="C39" s="28" t="s">
-        <v>170</v>
-      </c>
-      <c r="D39" s="28"/>
-      <c r="E39" s="29"/>
+    <row r="39" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="H39" s="3" t="s">
         <v>67</v>
       </c>
@@ -2436,18 +2460,14 @@
       <c r="K39" s="4"/>
     </row>
     <row r="40" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B40" s="30" t="s">
-        <v>55</v>
-      </c>
-      <c r="C40" s="31" t="s">
-        <v>106</v>
-      </c>
-      <c r="D40" s="31" t="s">
-        <v>107</v>
-      </c>
-      <c r="E40" s="32" t="s">
-        <v>108</v>
-      </c>
+      <c r="B40" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="C40" s="28" t="s">
+        <v>170</v>
+      </c>
+      <c r="D40" s="28"/>
+      <c r="E40" s="29"/>
       <c r="H40" s="3" t="s">
         <v>29</v>
       </c>
@@ -2460,17 +2480,17 @@
       <c r="K40" s="4"/>
     </row>
     <row r="41" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B41" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="E41" s="22" t="s">
-        <v>110</v>
+      <c r="B41" s="30" t="s">
+        <v>55</v>
+      </c>
+      <c r="C41" s="31" t="s">
+        <v>106</v>
+      </c>
+      <c r="D41" s="31" t="s">
+        <v>107</v>
+      </c>
+      <c r="E41" s="32" t="s">
+        <v>108</v>
       </c>
       <c r="H41" s="3" t="s">
         <v>137</v>
@@ -2487,16 +2507,16 @@
     </row>
     <row r="42" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B42" s="3" t="s">
-        <v>46</v>
+        <v>203</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="E42" s="4" t="s">
-        <v>119</v>
+        <v>80</v>
+      </c>
+      <c r="E42" s="22" t="s">
+        <v>110</v>
       </c>
       <c r="H42" s="3" t="s">
         <v>28</v>
@@ -2511,13 +2531,13 @@
     </row>
     <row r="43" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B43" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E43" s="4" t="s">
         <v>119</v>
@@ -2537,43 +2557,43 @@
     </row>
     <row r="44" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B44" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D44" s="1" t="s">
         <v>80</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>175</v>
+        <v>119</v>
       </c>
     </row>
     <row r="45" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B45" s="3" t="s">
-        <v>97</v>
+        <v>48</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="D45" t="s">
-        <v>201</v>
-      </c>
-      <c r="E45" s="4"/>
+        <v>174</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="E45" s="4" t="s">
+        <v>175</v>
+      </c>
     </row>
     <row r="46" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B46" s="3" t="s">
-        <v>162</v>
+        <v>97</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="D46" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="E46" s="4" t="s">
-        <v>175</v>
-      </c>
+        <v>176</v>
+      </c>
+      <c r="D46" t="s">
+        <v>201</v>
+      </c>
+      <c r="E46" s="4"/>
       <c r="H46" s="27" t="s">
         <v>143</v>
       </c>
@@ -2583,17 +2603,19 @@
       <c r="J46" s="28"/>
       <c r="K46" s="29"/>
     </row>
-    <row r="47" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B47" s="5" t="s">
-        <v>178</v>
-      </c>
-      <c r="C47" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="D47" s="35" t="s">
-        <v>96</v>
-      </c>
-      <c r="E47" s="7"/>
+    <row r="47" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B47" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="E47" s="4" t="s">
+        <v>175</v>
+      </c>
       <c r="H47" s="30" t="s">
         <v>55</v>
       </c>
@@ -2608,6 +2630,16 @@
       </c>
     </row>
     <row r="48" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B48" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="C48" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="D48" s="35" t="s">
+        <v>96</v>
+      </c>
+      <c r="E48" s="7"/>
       <c r="H48" s="3" t="s">
         <v>209</v>
       </c>
@@ -2621,15 +2653,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="49" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B49" s="27" t="s">
-        <v>20</v>
-      </c>
-      <c r="C49" s="28" t="s">
-        <v>180</v>
-      </c>
-      <c r="D49" s="28"/>
-      <c r="E49" s="29"/>
+    <row r="49" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="H49" s="3" t="s">
         <v>65</v>
       </c>
@@ -2644,18 +2668,14 @@
       </c>
     </row>
     <row r="50" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B50" s="30" t="s">
-        <v>55</v>
-      </c>
-      <c r="C50" s="31" t="s">
-        <v>106</v>
-      </c>
-      <c r="D50" s="31" t="s">
-        <v>107</v>
-      </c>
-      <c r="E50" s="32" t="s">
-        <v>108</v>
-      </c>
+      <c r="B50" s="27" t="s">
+        <v>20</v>
+      </c>
+      <c r="C50" s="28" t="s">
+        <v>180</v>
+      </c>
+      <c r="D50" s="28"/>
+      <c r="E50" s="29"/>
       <c r="H50" s="3" t="s">
         <v>67</v>
       </c>
@@ -2668,17 +2688,17 @@
       <c r="K50" s="4"/>
     </row>
     <row r="51" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B51" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="C51" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="D51" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="E51" s="23" t="s">
-        <v>200</v>
+      <c r="B51" s="30" t="s">
+        <v>55</v>
+      </c>
+      <c r="C51" s="31" t="s">
+        <v>106</v>
+      </c>
+      <c r="D51" s="31" t="s">
+        <v>107</v>
+      </c>
+      <c r="E51" s="32" t="s">
+        <v>108</v>
       </c>
       <c r="H51" s="3" t="s">
         <v>208</v>
@@ -2695,10 +2715,10 @@
     </row>
     <row r="52" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B52" s="3" t="s">
-        <v>52</v>
+        <v>205</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>165</v>
+        <v>109</v>
       </c>
       <c r="D52" s="1" t="s">
         <v>80</v>
@@ -2721,27 +2741,41 @@
     </row>
     <row r="53" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B53" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="E53" s="23" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="54" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B54" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="C53" s="1" t="s">
+      <c r="C54" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="D53" s="1" t="s">
+      <c r="D54" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="E53" s="4"/>
-    </row>
-    <row r="54" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B54" s="36" t="s">
+      <c r="E54" s="4"/>
+    </row>
+    <row r="55" spans="2:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B55" s="36" t="s">
         <v>211</v>
       </c>
-      <c r="C54" s="37" t="s">
+      <c r="C55" s="37" t="s">
         <v>212</v>
       </c>
-      <c r="D54" s="37" t="s">
+      <c r="D55" s="37" t="s">
         <v>83</v>
       </c>
-      <c r="E54" s="38" t="s">
+      <c r="E55" s="38" t="s">
         <v>131</v>
       </c>
     </row>
